--- a/dps_params.xlsx
+++ b/dps_params.xlsx
@@ -463,7 +463,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>-305.6340637207031</v>
+        <v>-312.7757873535156</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>-130.1778717041016</v>
+        <v>-131.5140838623047</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-81.9305419921875</v>
+        <v>-75.88648986816406</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-90.91542816162109</v>
+        <v>-94.108154296875</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>-282.8049621582031</v>
+        <v>-280.8714599609375</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-84.22756958007812</v>
+        <v>-85.23464202880859</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-72.88702392578125</v>
+        <v>-67.84782409667969</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-74.25981140136719</v>
+        <v>-77.71986389160156</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-63.81476593017578</v>
+        <v>-70.32724761962891</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-77.47400665283203</v>
+        <v>-75.32581329345703</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-249.8997192382812</v>
+        <v>-236.6942291259766</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-83.67510223388672</v>
+        <v>-79.01725006103516</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-160.2176666259766</v>
+        <v>-162.1633453369141</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-84.71324920654297</v>
+        <v>-82.53616333007812</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-82.30638885498047</v>
+        <v>-76.85581970214844</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-138.4966583251953</v>
+        <v>-141.9286651611328</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>-171.8404235839844</v>
+        <v>-172.1657104492188</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-90.90493011474609</v>
+        <v>-85.7677001953125</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>-129.6206207275391</v>
+        <v>-133.7468719482422</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-76.56881713867188</v>
+        <v>-75.62960815429688</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>-155.6732635498047</v>
+        <v>-153.9105224609375</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-77.12702941894531</v>
+        <v>-80.67966461181641</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-77.58208465576172</v>
+        <v>-84.42353820800781</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-75.69430541992188</v>
+        <v>-82.71511077880859</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-79.89360809326172</v>
+        <v>-81.03924560546875</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>-300.4434814453125</v>
+        <v>-304.7581787109375</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>-157.4926147460938</v>
+        <v>-160.8372344970703</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>-278.3193664550781</v>
+        <v>-283.3493041992188</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>-287.529541015625</v>
+        <v>-293.1230773925781</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-82.58261871337891</v>
+        <v>-87.68689727783203</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-65.47367858886719</v>
+        <v>-66.42996215820312</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +959,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>-242.3220367431641</v>
+        <v>-238.8040161132812</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +975,7 @@
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>-269.9835205078125</v>
+        <v>-273.1069030761719</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-87.49224853515625</v>
+        <v>-86.92874145507812</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-79.66177368164062</v>
+        <v>-79.61103820800781</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>-143.4646606445312</v>
+        <v>-147.7962493896484</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>-132.6531066894531</v>
+        <v>-139.0652770996094</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>-78.58596801757812</v>
+        <v>-80.14743041992188</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>-146.6327667236328</v>
+        <v>-143.899169921875</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>-138.8265533447266</v>
+        <v>-137.2330780029297</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1103,7 @@
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>-87.00629425048828</v>
+        <v>-89.46537780761719</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>-82.85569763183594</v>
+        <v>-78.8984375</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>-153.6828918457031</v>
+        <v>-149.2513885498047</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1151,7 @@
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>-73.60598754882812</v>
+        <v>-79.52750396728516</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1167,7 @@
         <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>-308.3492126464844</v>
+        <v>-301.6453857421875</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1183,7 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>-74.75551605224609</v>
+        <v>-80.38056182861328</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>-255.5670013427734</v>
+        <v>-251.2189788818359</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1215,7 @@
         <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>-230.8513488769531</v>
+        <v>-222.1041107177734</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1231,7 @@
         <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>-149.5818328857422</v>
+        <v>-140.1507568359375</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1247,7 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>-78.25110626220703</v>
+        <v>-79.82917022705078</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1263,7 @@
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>-151.075927734375</v>
+        <v>-146.8721313476562</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1279,7 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>-78.03773498535156</v>
+        <v>-83.03791809082031</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1295,7 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>-88.36556243896484</v>
+        <v>-88.17540740966797</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>-170.2906036376953</v>
+        <v>-170.7767181396484</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1327,7 @@
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>-141.3335876464844</v>
+        <v>-140.1629943847656</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1343,7 @@
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>-77.85420227050781</v>
+        <v>-79.80036163330078</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1359,7 @@
         <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>-234.7734222412109</v>
+        <v>-242.427001953125</v>
       </c>
     </row>
     <row r="59">
@@ -1375,7 +1375,7 @@
         <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>-127.860595703125</v>
+        <v>-127.6919860839844</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1391,7 @@
         <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>-250.8308410644531</v>
+        <v>-258.9580078125</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1407,7 @@
         <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>-168.5839233398438</v>
+        <v>-172.2892150878906</v>
       </c>
     </row>
     <row r="62">
@@ -1423,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>-84.57220458984375</v>
+        <v>-85.5037841796875</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1439,7 @@
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>-114.2325286865234</v>
+        <v>-118.6301956176758</v>
       </c>
     </row>
     <row r="64">
@@ -1455,7 +1455,7 @@
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>-82.19145202636719</v>
+        <v>-83.99555206298828</v>
       </c>
     </row>
     <row r="65">
@@ -1471,7 +1471,7 @@
         <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>-176.1431427001953</v>
+        <v>-168.9671173095703</v>
       </c>
     </row>
     <row r="66">
@@ -1487,7 +1487,7 @@
         <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>-137.8791046142578</v>
+        <v>-128.9008483886719</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1503,7 @@
         <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>-135.71142578125</v>
+        <v>-140.9709320068359</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1519,7 @@
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>-84.24828338623047</v>
+        <v>-78.59947967529297</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1535,7 @@
         <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>-137.4445953369141</v>
+        <v>-139.8025665283203</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1551,7 @@
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>-77.77011108398438</v>
+        <v>-76.41378784179688</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1567,7 @@
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>-84.24244689941406</v>
+        <v>-81.67057037353516</v>
       </c>
     </row>
     <row r="72">
@@ -1583,7 +1583,7 @@
         <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>-325.7579040527344</v>
+        <v>-328.6674499511719</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1599,7 @@
         <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>-128.9672088623047</v>
+        <v>-134.2458648681641</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1615,7 @@
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>-78.30921936035156</v>
+        <v>-74.20224761962891</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1631,7 @@
         <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>-125.3225402832031</v>
+        <v>-118.1796340942383</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1647,7 @@
         <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>-127.3885498046875</v>
+        <v>-123.8785781860352</v>
       </c>
     </row>
     <row r="77">
@@ -1663,7 +1663,7 @@
         <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>-249.2862243652344</v>
+        <v>-247.5622711181641</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1679,7 @@
         <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>-156.5807800292969</v>
+        <v>-154.4074554443359</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1695,7 @@
         <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>-152.9647216796875</v>
+        <v>-146.2172393798828</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1711,7 @@
         <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>-154.9695281982422</v>
+        <v>-159.734130859375</v>
       </c>
     </row>
     <row r="81">
@@ -1727,7 +1727,7 @@
         <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>-208.3752746582031</v>
+        <v>-217.0181427001953</v>
       </c>
     </row>
     <row r="82">
@@ -1743,7 +1743,7 @@
         <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>-154.9638214111328</v>
+        <v>-153.9062652587891</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1759,7 @@
         <v>4</v>
       </c>
       <c r="D83" t="n">
-        <v>-319.77783203125</v>
+        <v>-321.4641723632812</v>
       </c>
     </row>
     <row r="84">
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>-92.42150115966797</v>
+        <v>-89.32257843017578</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1791,7 @@
         <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>-142.9005737304688</v>
+        <v>-141.1580200195312</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1807,7 @@
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>-70.63034820556641</v>
+        <v>-76.47366333007812</v>
       </c>
     </row>
     <row r="87">
@@ -1823,7 +1823,7 @@
         <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>-121.7879638671875</v>
+        <v>-126.2312545776367</v>
       </c>
     </row>
     <row r="88">
@@ -1839,7 +1839,7 @@
         <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>-144.2102813720703</v>
+        <v>-146.6411437988281</v>
       </c>
     </row>
     <row r="89">
@@ -1855,7 +1855,7 @@
         <v>4</v>
       </c>
       <c r="D89" t="n">
-        <v>-277.3495788574219</v>
+        <v>-281.5845031738281</v>
       </c>
     </row>
     <row r="90">
@@ -1871,7 +1871,7 @@
         <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>-158.7028961181641</v>
+        <v>-158.1317291259766</v>
       </c>
     </row>
     <row r="91">
@@ -1887,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>-80.64934539794922</v>
+        <v>-83.46322631835938</v>
       </c>
     </row>
     <row r="92">
@@ -1903,7 +1903,7 @@
         <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>-147.6284484863281</v>
+        <v>-142.9967346191406</v>
       </c>
     </row>
     <row r="93">
@@ -1919,7 +1919,7 @@
         <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>-134.8853302001953</v>
+        <v>-136.2752685546875</v>
       </c>
     </row>
     <row r="94">
@@ -1935,7 +1935,7 @@
         <v>4</v>
       </c>
       <c r="D94" t="n">
-        <v>-284.679443359375</v>
+        <v>-287.8291931152344</v>
       </c>
     </row>
     <row r="95">
@@ -1951,7 +1951,7 @@
         <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>-139.9490203857422</v>
+        <v>-133.0659637451172</v>
       </c>
     </row>
     <row r="96">
@@ -1967,7 +1967,7 @@
         <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>-138.0877227783203</v>
+        <v>-137.7978210449219</v>
       </c>
     </row>
     <row r="97">
@@ -1983,7 +1983,7 @@
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>-79.82749938964844</v>
+        <v>-77.16901397705078</v>
       </c>
     </row>
     <row r="98">
@@ -1999,7 +1999,7 @@
         <v>2</v>
       </c>
       <c r="D98" t="n">
-        <v>-137.2913665771484</v>
+        <v>-142.02197265625</v>
       </c>
     </row>
     <row r="99">
@@ -2015,7 +2015,7 @@
         <v>2</v>
       </c>
       <c r="D99" t="n">
-        <v>-160.7830200195312</v>
+        <v>-152.9811248779297</v>
       </c>
     </row>
     <row r="100">
@@ -2031,7 +2031,7 @@
         <v>2</v>
       </c>
       <c r="D100" t="n">
-        <v>-162.2740325927734</v>
+        <v>-165.0660858154297</v>
       </c>
     </row>
     <row r="101">
@@ -2047,7 +2047,7 @@
         <v>4</v>
       </c>
       <c r="D101" t="n">
-        <v>-267.9410705566406</v>
+        <v>-268.0858764648438</v>
       </c>
     </row>
     <row r="102">
@@ -2063,7 +2063,7 @@
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>-83.00568389892578</v>
+        <v>-84.41999816894531</v>
       </c>
     </row>
     <row r="103">
@@ -2079,7 +2079,7 @@
         <v>2</v>
       </c>
       <c r="D103" t="n">
-        <v>-115.7213668823242</v>
+        <v>-114.7257080078125</v>
       </c>
     </row>
     <row r="104">
@@ -2095,7 +2095,7 @@
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>-77.21486663818359</v>
+        <v>-83.75466156005859</v>
       </c>
     </row>
     <row r="105">
@@ -2111,7 +2111,7 @@
         <v>2</v>
       </c>
       <c r="D105" t="n">
-        <v>-157.4570770263672</v>
+        <v>-156.8981170654297</v>
       </c>
     </row>
     <row r="106">
@@ -2127,7 +2127,7 @@
         <v>2</v>
       </c>
       <c r="D106" t="n">
-        <v>-117.9080200195312</v>
+        <v>-120.8911209106445</v>
       </c>
     </row>
     <row r="107">
@@ -2143,7 +2143,7 @@
         <v>2</v>
       </c>
       <c r="D107" t="n">
-        <v>-154.2335815429688</v>
+        <v>-155.3239898681641</v>
       </c>
     </row>
     <row r="108">
@@ -2159,7 +2159,7 @@
         <v>4</v>
       </c>
       <c r="D108" t="n">
-        <v>-301.8592834472656</v>
+        <v>-303.7877502441406</v>
       </c>
     </row>
     <row r="109">
@@ -2175,7 +2175,7 @@
         <v>2</v>
       </c>
       <c r="D109" t="n">
-        <v>-122.5231094360352</v>
+        <v>-125.7340393066406</v>
       </c>
     </row>
     <row r="110">
@@ -2191,7 +2191,7 @@
         <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>-85.62743377685547</v>
+        <v>-89.494384765625</v>
       </c>
     </row>
     <row r="111">
@@ -2207,7 +2207,7 @@
         <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>-73.16877746582031</v>
+        <v>-80.56299591064453</v>
       </c>
     </row>
     <row r="112">
@@ -2223,7 +2223,7 @@
         <v>2</v>
       </c>
       <c r="D112" t="n">
-        <v>-125.7355651855469</v>
+        <v>-124.9062347412109</v>
       </c>
     </row>
     <row r="113">
@@ -2239,7 +2239,7 @@
         <v>2</v>
       </c>
       <c r="D113" t="n">
-        <v>-166.2066497802734</v>
+        <v>-166.9066925048828</v>
       </c>
     </row>
     <row r="114">
@@ -2255,7 +2255,7 @@
         <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>-91.13640594482422</v>
+        <v>-84.74359893798828</v>
       </c>
     </row>
     <row r="115">
@@ -2271,7 +2271,7 @@
         <v>4</v>
       </c>
       <c r="D115" t="n">
-        <v>-317.3254699707031</v>
+        <v>-313.0737609863281</v>
       </c>
     </row>
     <row r="116">
@@ -2287,7 +2287,7 @@
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>-86.65670013427734</v>
+        <v>-83.99855041503906</v>
       </c>
     </row>
     <row r="117">
@@ -2303,7 +2303,7 @@
         <v>4</v>
       </c>
       <c r="D117" t="n">
-        <v>-328.5519714355469</v>
+        <v>-328.6477966308594</v>
       </c>
     </row>
     <row r="118">
@@ -2319,7 +2319,7 @@
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>-73.92996215820312</v>
+        <v>-76.95477294921875</v>
       </c>
     </row>
     <row r="119">
@@ -2335,7 +2335,7 @@
         <v>4</v>
       </c>
       <c r="D119" t="n">
-        <v>-303.5566711425781</v>
+        <v>-295.3050537109375</v>
       </c>
     </row>
     <row r="120">
@@ -2351,7 +2351,7 @@
         <v>2</v>
       </c>
       <c r="D120" t="n">
-        <v>-153.5810852050781</v>
+        <v>-153.3857269287109</v>
       </c>
     </row>
     <row r="121">
@@ -2367,7 +2367,7 @@
         <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>-81.44486236572266</v>
+        <v>-82.38832855224609</v>
       </c>
     </row>
     <row r="122">
@@ -2383,7 +2383,7 @@
         <v>2</v>
       </c>
       <c r="D122" t="n">
-        <v>-168.2002410888672</v>
+        <v>-164.2074432373047</v>
       </c>
     </row>
     <row r="123">
@@ -2399,7 +2399,7 @@
         <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>-79.39560699462891</v>
+        <v>-76.27633666992188</v>
       </c>
     </row>
     <row r="124">
@@ -2415,7 +2415,7 @@
         <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>-79.90325927734375</v>
+        <v>-76.79575347900391</v>
       </c>
     </row>
     <row r="125">
@@ -2431,7 +2431,7 @@
         <v>2</v>
       </c>
       <c r="D125" t="n">
-        <v>-151.8598937988281</v>
+        <v>-149.9316558837891</v>
       </c>
     </row>
     <row r="126">
@@ -2447,7 +2447,7 @@
         <v>2</v>
       </c>
       <c r="D126" t="n">
-        <v>-156.3366546630859</v>
+        <v>-160.6572723388672</v>
       </c>
     </row>
     <row r="127">
@@ -2463,7 +2463,7 @@
         <v>2</v>
       </c>
       <c r="D127" t="n">
-        <v>-111.4025955200195</v>
+        <v>-111.4554901123047</v>
       </c>
     </row>
     <row r="128">
@@ -2479,7 +2479,7 @@
         <v>2</v>
       </c>
       <c r="D128" t="n">
-        <v>-158.3274536132812</v>
+        <v>-159.4218292236328</v>
       </c>
     </row>
     <row r="129">
@@ -2495,7 +2495,7 @@
         <v>4</v>
       </c>
       <c r="D129" t="n">
-        <v>-314.4833679199219</v>
+        <v>-320.92041015625</v>
       </c>
     </row>
     <row r="130">
@@ -2511,7 +2511,7 @@
         <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>-77.28602600097656</v>
+        <v>-74.76960754394531</v>
       </c>
     </row>
     <row r="131">
@@ -2527,7 +2527,7 @@
         <v>1</v>
       </c>
       <c r="D131" t="n">
-        <v>-81.45471954345703</v>
+        <v>-79.46607208251953</v>
       </c>
     </row>
     <row r="132">
@@ -2543,7 +2543,7 @@
         <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>-76.83599853515625</v>
+        <v>-77.08785247802734</v>
       </c>
     </row>
     <row r="133">
@@ -2559,7 +2559,7 @@
         <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>-87.41319274902344</v>
+        <v>-82.26343536376953</v>
       </c>
     </row>
     <row r="134">
@@ -2575,7 +2575,7 @@
         <v>1</v>
       </c>
       <c r="D134" t="n">
-        <v>-67.08291625976562</v>
+        <v>-65.56641387939453</v>
       </c>
     </row>
     <row r="135">
@@ -2591,7 +2591,7 @@
         <v>4</v>
       </c>
       <c r="D135" t="n">
-        <v>-288.8900451660156</v>
+        <v>-287.2226257324219</v>
       </c>
     </row>
     <row r="136">
@@ -2607,7 +2607,7 @@
         <v>4</v>
       </c>
       <c r="D136" t="n">
-        <v>-276.09228515625</v>
+        <v>-279.2212219238281</v>
       </c>
     </row>
     <row r="137">
@@ -2623,7 +2623,7 @@
         <v>2</v>
       </c>
       <c r="D137" t="n">
-        <v>-154.6051330566406</v>
+        <v>-146.6395568847656</v>
       </c>
     </row>
     <row r="138">
@@ -2639,7 +2639,7 @@
         <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>-75.9322509765625</v>
+        <v>-76.14176177978516</v>
       </c>
     </row>
     <row r="139">
@@ -2655,7 +2655,7 @@
         <v>4</v>
       </c>
       <c r="D139" t="n">
-        <v>-290.0324401855469</v>
+        <v>-283.7652893066406</v>
       </c>
     </row>
     <row r="140">
@@ -2671,7 +2671,7 @@
         <v>2</v>
       </c>
       <c r="D140" t="n">
-        <v>-116.9782485961914</v>
+        <v>-112.6419372558594</v>
       </c>
     </row>
     <row r="141">
@@ -2687,7 +2687,7 @@
         <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>-84.98077392578125</v>
+        <v>-88.72606658935547</v>
       </c>
     </row>
     <row r="142">
@@ -2703,7 +2703,7 @@
         <v>2</v>
       </c>
       <c r="D142" t="n">
-        <v>-151.0917663574219</v>
+        <v>-154.3799133300781</v>
       </c>
     </row>
     <row r="143">
@@ -2719,7 +2719,7 @@
         <v>2</v>
       </c>
       <c r="D143" t="n">
-        <v>-145.5934448242188</v>
+        <v>-141.1440124511719</v>
       </c>
     </row>
     <row r="144">
@@ -2735,7 +2735,7 @@
         <v>4</v>
       </c>
       <c r="D144" t="n">
-        <v>-269.60791015625</v>
+        <v>-271.1011047363281</v>
       </c>
     </row>
     <row r="145">
@@ -2751,7 +2751,7 @@
         <v>2</v>
       </c>
       <c r="D145" t="n">
-        <v>-128.2825317382812</v>
+        <v>-122.1092147827148</v>
       </c>
     </row>
     <row r="146">
@@ -2767,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>-79.21617889404297</v>
+        <v>-76.92984008789062</v>
       </c>
     </row>
     <row r="147">
@@ -2783,7 +2783,7 @@
         <v>2</v>
       </c>
       <c r="D147" t="n">
-        <v>-167.4762878417969</v>
+        <v>-166.9119720458984</v>
       </c>
     </row>
     <row r="148">
@@ -2799,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>-81.75291442871094</v>
+        <v>-77.52755737304688</v>
       </c>
     </row>
     <row r="149">
@@ -2815,7 +2815,7 @@
         <v>4</v>
       </c>
       <c r="D149" t="n">
-        <v>-266.0339050292969</v>
+        <v>-262.2939453125</v>
       </c>
     </row>
     <row r="150">
@@ -2831,7 +2831,7 @@
         <v>2</v>
       </c>
       <c r="D150" t="n">
-        <v>-151.1453247070312</v>
+        <v>-157.6202087402344</v>
       </c>
     </row>
     <row r="151">
@@ -2847,7 +2847,7 @@
         <v>2</v>
       </c>
       <c r="D151" t="n">
-        <v>-135.6094665527344</v>
+        <v>-129.8075714111328</v>
       </c>
     </row>
     <row r="152">
@@ -2863,7 +2863,7 @@
         <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>-80.48418426513672</v>
+        <v>-83.51857757568359</v>
       </c>
     </row>
     <row r="153">
@@ -2879,7 +2879,7 @@
         <v>2</v>
       </c>
       <c r="D153" t="n">
-        <v>-140.8275756835938</v>
+        <v>-136.2218322753906</v>
       </c>
     </row>
     <row r="154">
@@ -2895,7 +2895,7 @@
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>-76.68886566162109</v>
+        <v>-81.11664581298828</v>
       </c>
     </row>
     <row r="155">
@@ -2911,7 +2911,7 @@
         <v>2</v>
       </c>
       <c r="D155" t="n">
-        <v>-117.5181274414062</v>
+        <v>-124.919677734375</v>
       </c>
     </row>
     <row r="156">
@@ -2927,7 +2927,7 @@
         <v>2</v>
       </c>
       <c r="D156" t="n">
-        <v>-153.4190063476562</v>
+        <v>-150.9056243896484</v>
       </c>
     </row>
     <row r="157">
@@ -2943,7 +2943,7 @@
         <v>2</v>
       </c>
       <c r="D157" t="n">
-        <v>-160.3657073974609</v>
+        <v>-166.4950256347656</v>
       </c>
     </row>
     <row r="158">
@@ -2959,7 +2959,7 @@
         <v>4</v>
       </c>
       <c r="D158" t="n">
-        <v>-222.7861633300781</v>
+        <v>-221.5299682617188</v>
       </c>
     </row>
     <row r="159">
@@ -2975,7 +2975,7 @@
         <v>2</v>
       </c>
       <c r="D159" t="n">
-        <v>-160.54150390625</v>
+        <v>-161.8446197509766</v>
       </c>
     </row>
     <row r="160">
@@ -2991,7 +2991,7 @@
         <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>-81.79920959472656</v>
+        <v>-77.48191833496094</v>
       </c>
     </row>
     <row r="161">
@@ -3007,7 +3007,7 @@
         <v>2</v>
       </c>
       <c r="D161" t="n">
-        <v>-162.1113433837891</v>
+        <v>-165.3515625</v>
       </c>
     </row>
     <row r="162">
@@ -3023,7 +3023,7 @@
         <v>2</v>
       </c>
       <c r="D162" t="n">
-        <v>-168.2012023925781</v>
+        <v>-168.0431976318359</v>
       </c>
     </row>
     <row r="163">
@@ -3039,7 +3039,7 @@
         <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>-82.82553863525391</v>
+        <v>-78.96121215820312</v>
       </c>
     </row>
     <row r="164">
@@ -3055,7 +3055,7 @@
         <v>2</v>
       </c>
       <c r="D164" t="n">
-        <v>-140.585205078125</v>
+        <v>-140.8423309326172</v>
       </c>
     </row>
     <row r="165">
@@ -3071,7 +3071,7 @@
         <v>2</v>
       </c>
       <c r="D165" t="n">
-        <v>-147.0983734130859</v>
+        <v>-142.3974761962891</v>
       </c>
     </row>
     <row r="166">
@@ -3087,7 +3087,7 @@
         <v>2</v>
       </c>
       <c r="D166" t="n">
-        <v>-115.2877044677734</v>
+        <v>-123.1963348388672</v>
       </c>
     </row>
     <row r="167">
@@ -3103,7 +3103,7 @@
         <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>-69.262939453125</v>
+        <v>-68.05825805664062</v>
       </c>
     </row>
     <row r="168">
@@ -3119,7 +3119,7 @@
         <v>2</v>
       </c>
       <c r="D168" t="n">
-        <v>-154.2197723388672</v>
+        <v>-150.4101257324219</v>
       </c>
     </row>
     <row r="169">
@@ -3135,7 +3135,7 @@
         <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>-72.36476135253906</v>
+        <v>-72.12531280517578</v>
       </c>
     </row>
     <row r="170">
@@ -3151,7 +3151,7 @@
         <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>-78.97440338134766</v>
+        <v>-81.53610992431641</v>
       </c>
     </row>
     <row r="171">
@@ -3167,7 +3167,7 @@
         <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>-95.71196746826172</v>
+        <v>-94.9534912109375</v>
       </c>
     </row>
     <row r="172">
@@ -3183,7 +3183,7 @@
         <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>-80.86284637451172</v>
+        <v>-81.673095703125</v>
       </c>
     </row>
     <row r="173">
@@ -3199,7 +3199,7 @@
         <v>4</v>
       </c>
       <c r="D173" t="n">
-        <v>-300.4794311523438</v>
+        <v>-311.0089111328125</v>
       </c>
     </row>
     <row r="174">
@@ -3215,7 +3215,7 @@
         <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>-85.44883728027344</v>
+        <v>-83.23433685302734</v>
       </c>
     </row>
     <row r="175">
@@ -3231,7 +3231,7 @@
         <v>2</v>
       </c>
       <c r="D175" t="n">
-        <v>-160.8102874755859</v>
+        <v>-159.924560546875</v>
       </c>
     </row>
     <row r="176">
@@ -3247,7 +3247,7 @@
         <v>4</v>
       </c>
       <c r="D176" t="n">
-        <v>-297.2001342773438</v>
+        <v>-291.809326171875</v>
       </c>
     </row>
     <row r="177">
@@ -3263,7 +3263,7 @@
         <v>2</v>
       </c>
       <c r="D177" t="n">
-        <v>-135.5363922119141</v>
+        <v>-132.9282379150391</v>
       </c>
     </row>
     <row r="178">
@@ -3279,7 +3279,7 @@
         <v>2</v>
       </c>
       <c r="D178" t="n">
-        <v>-152.6901092529297</v>
+        <v>-156.6605529785156</v>
       </c>
     </row>
     <row r="179">
@@ -3295,7 +3295,7 @@
         <v>4</v>
       </c>
       <c r="D179" t="n">
-        <v>-297.9146423339844</v>
+        <v>-304.3961791992188</v>
       </c>
     </row>
     <row r="180">
@@ -3311,7 +3311,7 @@
         <v>2</v>
       </c>
       <c r="D180" t="n">
-        <v>-159.8001861572266</v>
+        <v>-156.9090881347656</v>
       </c>
     </row>
     <row r="181">
@@ -3327,7 +3327,7 @@
         <v>1</v>
       </c>
       <c r="D181" t="n">
-        <v>-86.69662475585938</v>
+        <v>-83.38128662109375</v>
       </c>
     </row>
     <row r="182">
@@ -3343,7 +3343,7 @@
         <v>2</v>
       </c>
       <c r="D182" t="n">
-        <v>-122.6481323242188</v>
+        <v>-130.5007476806641</v>
       </c>
     </row>
     <row r="183">
@@ -3359,7 +3359,7 @@
         <v>1</v>
       </c>
       <c r="D183" t="n">
-        <v>-77.53282165527344</v>
+        <v>-79.68167114257812</v>
       </c>
     </row>
     <row r="184">
@@ -3375,7 +3375,7 @@
         <v>4</v>
       </c>
       <c r="D184" t="n">
-        <v>-218.3810119628906</v>
+        <v>-223.1823577880859</v>
       </c>
     </row>
     <row r="185">
@@ -3391,7 +3391,7 @@
         <v>2</v>
       </c>
       <c r="D185" t="n">
-        <v>-163.7280731201172</v>
+        <v>-164.4349670410156</v>
       </c>
     </row>
     <row r="186">
@@ -3407,7 +3407,7 @@
         <v>2</v>
       </c>
       <c r="D186" t="n">
-        <v>-143.3491668701172</v>
+        <v>-147.9378051757812</v>
       </c>
     </row>
     <row r="187">
@@ -3423,7 +3423,7 @@
         <v>2</v>
       </c>
       <c r="D187" t="n">
-        <v>-157.4538421630859</v>
+        <v>-159.9310913085938</v>
       </c>
     </row>
     <row r="188">
@@ -3439,7 +3439,7 @@
         <v>2</v>
       </c>
       <c r="D188" t="n">
-        <v>-146.822509765625</v>
+        <v>-144.5268249511719</v>
       </c>
     </row>
     <row r="189">
@@ -3455,7 +3455,7 @@
         <v>1</v>
       </c>
       <c r="D189" t="n">
-        <v>-71.25525665283203</v>
+        <v>-72.51679992675781</v>
       </c>
     </row>
     <row r="190">
@@ -3471,7 +3471,7 @@
         <v>4</v>
       </c>
       <c r="D190" t="n">
-        <v>-254.5234222412109</v>
+        <v>-263.9480590820312</v>
       </c>
     </row>
     <row r="191">
@@ -3487,7 +3487,7 @@
         <v>2</v>
       </c>
       <c r="D191" t="n">
-        <v>-118.5180282592773</v>
+        <v>-124.8707122802734</v>
       </c>
     </row>
     <row r="192">
@@ -3503,7 +3503,7 @@
         <v>1</v>
       </c>
       <c r="D192" t="n">
-        <v>-78.8087158203125</v>
+        <v>-76.755615234375</v>
       </c>
     </row>
     <row r="193">
@@ -3519,7 +3519,7 @@
         <v>1</v>
       </c>
       <c r="D193" t="n">
-        <v>-86.58155822753906</v>
+        <v>-82.04090881347656</v>
       </c>
     </row>
     <row r="194">
@@ -3535,7 +3535,7 @@
         <v>2</v>
       </c>
       <c r="D194" t="n">
-        <v>-156.0891571044922</v>
+        <v>-155.453125</v>
       </c>
     </row>
     <row r="195">
@@ -3551,7 +3551,7 @@
         <v>4</v>
       </c>
       <c r="D195" t="n">
-        <v>-311.6601257324219</v>
+        <v>-303.3656005859375</v>
       </c>
     </row>
     <row r="196">
@@ -3567,7 +3567,7 @@
         <v>4</v>
       </c>
       <c r="D196" t="n">
-        <v>-332.464599609375</v>
+        <v>-320.0258483886719</v>
       </c>
     </row>
     <row r="197">
@@ -3583,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="D197" t="n">
-        <v>-80.23500823974609</v>
+        <v>-77.80377960205078</v>
       </c>
     </row>
     <row r="198">
@@ -3599,7 +3599,7 @@
         <v>2</v>
       </c>
       <c r="D198" t="n">
-        <v>-151.4332427978516</v>
+        <v>-155.2765502929688</v>
       </c>
     </row>
     <row r="199">
@@ -3615,7 +3615,7 @@
         <v>2</v>
       </c>
       <c r="D199" t="n">
-        <v>-121.5499877929688</v>
+        <v>-128.7712554931641</v>
       </c>
     </row>
     <row r="200">
@@ -3631,7 +3631,7 @@
         <v>2</v>
       </c>
       <c r="D200" t="n">
-        <v>-145.3911590576172</v>
+        <v>-139.4909820556641</v>
       </c>
     </row>
     <row r="201">
@@ -3647,7 +3647,7 @@
         <v>4</v>
       </c>
       <c r="D201" t="n">
-        <v>-321.6404113769531</v>
+        <v>-321.418701171875</v>
       </c>
     </row>
     <row r="202">
@@ -3663,7 +3663,7 @@
         <v>2</v>
       </c>
       <c r="D202" t="n">
-        <v>-156.7207946777344</v>
+        <v>-155.5260467529297</v>
       </c>
     </row>
     <row r="203">
@@ -3679,7 +3679,7 @@
         <v>1</v>
       </c>
       <c r="D203" t="n">
-        <v>-80.14970397949219</v>
+        <v>-79.34042358398438</v>
       </c>
     </row>
     <row r="204">
@@ -3695,7 +3695,7 @@
         <v>4</v>
       </c>
       <c r="D204" t="n">
-        <v>-298.0846557617188</v>
+        <v>-297.3146667480469</v>
       </c>
     </row>
     <row r="205">
@@ -3711,7 +3711,7 @@
         <v>1</v>
       </c>
       <c r="D205" t="n">
-        <v>-80.87654876708984</v>
+        <v>-82.83698272705078</v>
       </c>
     </row>
     <row r="206">
@@ -3727,7 +3727,7 @@
         <v>1</v>
       </c>
       <c r="D206" t="n">
-        <v>-83.09784698486328</v>
+        <v>-78.80796813964844</v>
       </c>
     </row>
     <row r="207">
@@ -3743,7 +3743,7 @@
         <v>2</v>
       </c>
       <c r="D207" t="n">
-        <v>-165.0968017578125</v>
+        <v>-167.9123077392578</v>
       </c>
     </row>
     <row r="208">
@@ -3759,7 +3759,7 @@
         <v>2</v>
       </c>
       <c r="D208" t="n">
-        <v>-126.5487899780273</v>
+        <v>-128.9845123291016</v>
       </c>
     </row>
     <row r="209">
@@ -3775,7 +3775,7 @@
         <v>2</v>
       </c>
       <c r="D209" t="n">
-        <v>-119.5523834228516</v>
+        <v>-126.9576950073242</v>
       </c>
     </row>
     <row r="210">
@@ -3791,7 +3791,7 @@
         <v>2</v>
       </c>
       <c r="D210" t="n">
-        <v>-149.3974761962891</v>
+        <v>-140.2644805908203</v>
       </c>
     </row>
     <row r="211">
@@ -3807,7 +3807,7 @@
         <v>2</v>
       </c>
       <c r="D211" t="n">
-        <v>-111.8229827880859</v>
+        <v>-109.3626327514648</v>
       </c>
     </row>
     <row r="212">
@@ -3823,7 +3823,7 @@
         <v>1</v>
       </c>
       <c r="D212" t="n">
-        <v>-90.33890533447266</v>
+        <v>-86.53759002685547</v>
       </c>
     </row>
     <row r="213">
@@ -3839,7 +3839,7 @@
         <v>1</v>
       </c>
       <c r="D213" t="n">
-        <v>-76.62405395507812</v>
+        <v>-73.15424346923828</v>
       </c>
     </row>
     <row r="214">
@@ -3855,7 +3855,7 @@
         <v>2</v>
       </c>
       <c r="D214" t="n">
-        <v>-150.6652221679688</v>
+        <v>-142.8046722412109</v>
       </c>
     </row>
     <row r="215">
@@ -3871,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="D215" t="n">
-        <v>-88.8721923828125</v>
+        <v>-95.81846618652344</v>
       </c>
     </row>
     <row r="216">
@@ -3887,7 +3887,7 @@
         <v>2</v>
       </c>
       <c r="D216" t="n">
-        <v>-150.655029296875</v>
+        <v>-148.0325469970703</v>
       </c>
     </row>
     <row r="217">
@@ -3903,7 +3903,7 @@
         <v>2</v>
       </c>
       <c r="D217" t="n">
-        <v>-139.6556854248047</v>
+        <v>-139.7101745605469</v>
       </c>
     </row>
     <row r="218">
@@ -3919,7 +3919,7 @@
         <v>2</v>
       </c>
       <c r="D218" t="n">
-        <v>-147.3952789306641</v>
+        <v>-148.0384216308594</v>
       </c>
     </row>
     <row r="219">
@@ -3935,7 +3935,7 @@
         <v>2</v>
       </c>
       <c r="D219" t="n">
-        <v>-131.5650634765625</v>
+        <v>-134.5567169189453</v>
       </c>
     </row>
     <row r="220">
@@ -3951,7 +3951,7 @@
         <v>2</v>
       </c>
       <c r="D220" t="n">
-        <v>-142.4123229980469</v>
+        <v>-143.5973815917969</v>
       </c>
     </row>
     <row r="221">
@@ -3967,7 +3967,7 @@
         <v>2</v>
       </c>
       <c r="D221" t="n">
-        <v>-152.7034912109375</v>
+        <v>-154.3467407226562</v>
       </c>
     </row>
     <row r="222">
@@ -3983,7 +3983,7 @@
         <v>2</v>
       </c>
       <c r="D222" t="n">
-        <v>-139.0016021728516</v>
+        <v>-143.9088592529297</v>
       </c>
     </row>
     <row r="223">
@@ -3999,7 +3999,7 @@
         <v>1</v>
       </c>
       <c r="D223" t="n">
-        <v>-92.83619689941406</v>
+        <v>-93.99896240234375</v>
       </c>
     </row>
     <row r="224">
@@ -4015,7 +4015,7 @@
         <v>1</v>
       </c>
       <c r="D224" t="n">
-        <v>-79.86627960205078</v>
+        <v>-78.56758117675781</v>
       </c>
     </row>
     <row r="225">
@@ -4031,7 +4031,7 @@
         <v>1</v>
       </c>
       <c r="D225" t="n">
-        <v>-82.56925964355469</v>
+        <v>-76.20285034179688</v>
       </c>
     </row>
     <row r="226">
@@ -4047,7 +4047,7 @@
         <v>2</v>
       </c>
       <c r="D226" t="n">
-        <v>-143.0322265625</v>
+        <v>-144.0987701416016</v>
       </c>
     </row>
     <row r="227">
@@ -4063,7 +4063,7 @@
         <v>1</v>
       </c>
       <c r="D227" t="n">
-        <v>-83.75398254394531</v>
+        <v>-87.01181030273438</v>
       </c>
     </row>
     <row r="228">
@@ -4079,7 +4079,7 @@
         <v>2</v>
       </c>
       <c r="D228" t="n">
-        <v>-150.6007080078125</v>
+        <v>-147.2466430664062</v>
       </c>
     </row>
     <row r="229">
@@ -4095,7 +4095,7 @@
         <v>1</v>
       </c>
       <c r="D229" t="n">
-        <v>-88.02726745605469</v>
+        <v>-89.93679809570312</v>
       </c>
     </row>
     <row r="230">
@@ -4111,7 +4111,7 @@
         <v>2</v>
       </c>
       <c r="D230" t="n">
-        <v>-130.8597869873047</v>
+        <v>-131.5619659423828</v>
       </c>
     </row>
     <row r="231">
@@ -4127,7 +4127,7 @@
         <v>2</v>
       </c>
       <c r="D231" t="n">
-        <v>-157.3708038330078</v>
+        <v>-161.1687316894531</v>
       </c>
     </row>
     <row r="232">
@@ -4143,7 +4143,7 @@
         <v>2</v>
       </c>
       <c r="D232" t="n">
-        <v>-138.0672454833984</v>
+        <v>-137.1577758789062</v>
       </c>
     </row>
     <row r="233">
@@ -4159,7 +4159,7 @@
         <v>2</v>
       </c>
       <c r="D233" t="n">
-        <v>-140.67822265625</v>
+        <v>-139.0460662841797</v>
       </c>
     </row>
     <row r="234">
@@ -4175,7 +4175,7 @@
         <v>4</v>
       </c>
       <c r="D234" t="n">
-        <v>-331.3232421875</v>
+        <v>-329.5998840332031</v>
       </c>
     </row>
     <row r="235">
@@ -4191,7 +4191,7 @@
         <v>4</v>
       </c>
       <c r="D235" t="n">
-        <v>-312.6475830078125</v>
+        <v>-312.3600463867188</v>
       </c>
     </row>
     <row r="236">
@@ -4207,7 +4207,7 @@
         <v>1</v>
       </c>
       <c r="D236" t="n">
-        <v>-86.226806640625</v>
+        <v>-84.76971435546875</v>
       </c>
     </row>
     <row r="237">
@@ -4223,7 +4223,7 @@
         <v>2</v>
       </c>
       <c r="D237" t="n">
-        <v>-132.89111328125</v>
+        <v>-131.4528961181641</v>
       </c>
     </row>
     <row r="238">
@@ -4239,7 +4239,7 @@
         <v>2</v>
       </c>
       <c r="D238" t="n">
-        <v>-163.9264831542969</v>
+        <v>-159.7869110107422</v>
       </c>
     </row>
     <row r="239">
@@ -4255,7 +4255,7 @@
         <v>4</v>
       </c>
       <c r="D239" t="n">
-        <v>-298.4087219238281</v>
+        <v>-302.4006958007812</v>
       </c>
     </row>
     <row r="240">
@@ -4271,7 +4271,7 @@
         <v>4</v>
       </c>
       <c r="D240" t="n">
-        <v>-325.4703674316406</v>
+        <v>-318.4396667480469</v>
       </c>
     </row>
     <row r="241">
@@ -4287,7 +4287,7 @@
         <v>4</v>
       </c>
       <c r="D241" t="n">
-        <v>-272.3374328613281</v>
+        <v>-271.9054565429688</v>
       </c>
     </row>
     <row r="242">
@@ -4303,7 +4303,7 @@
         <v>2</v>
       </c>
       <c r="D242" t="n">
-        <v>-171.0210418701172</v>
+        <v>-175.7023773193359</v>
       </c>
     </row>
     <row r="243">
@@ -4319,7 +4319,7 @@
         <v>2</v>
       </c>
       <c r="D243" t="n">
-        <v>-147.5235900878906</v>
+        <v>-146.3844299316406</v>
       </c>
     </row>
     <row r="244">
@@ -4335,7 +4335,7 @@
         <v>1</v>
       </c>
       <c r="D244" t="n">
-        <v>-81.16119384765625</v>
+        <v>-75.5706787109375</v>
       </c>
     </row>
     <row r="245">
@@ -4351,7 +4351,7 @@
         <v>4</v>
       </c>
       <c r="D245" t="n">
-        <v>-293.8094787597656</v>
+        <v>-304.7924194335938</v>
       </c>
     </row>
     <row r="246">
@@ -4367,7 +4367,7 @@
         <v>2</v>
       </c>
       <c r="D246" t="n">
-        <v>-131.8796539306641</v>
+        <v>-138.6028289794922</v>
       </c>
     </row>
     <row r="247">
@@ -4383,7 +4383,7 @@
         <v>2</v>
       </c>
       <c r="D247" t="n">
-        <v>-139.3135223388672</v>
+        <v>-143.3622894287109</v>
       </c>
     </row>
     <row r="248">
@@ -4399,7 +4399,7 @@
         <v>2</v>
       </c>
       <c r="D248" t="n">
-        <v>-167.1998443603516</v>
+        <v>-170.1062316894531</v>
       </c>
     </row>
     <row r="249">
@@ -4415,7 +4415,7 @@
         <v>4</v>
       </c>
       <c r="D249" t="n">
-        <v>-303.4909973144531</v>
+        <v>-291.0875244140625</v>
       </c>
     </row>
     <row r="250">
@@ -4431,7 +4431,7 @@
         <v>2</v>
       </c>
       <c r="D250" t="n">
-        <v>-138.0186767578125</v>
+        <v>-138.205078125</v>
       </c>
     </row>
     <row r="251">
@@ -4447,7 +4447,7 @@
         <v>4</v>
       </c>
       <c r="D251" t="n">
-        <v>-312.9636840820312</v>
+        <v>-304.9995727539062</v>
       </c>
     </row>
     <row r="252">
@@ -4463,7 +4463,7 @@
         <v>1</v>
       </c>
       <c r="D252" t="n">
-        <v>-79.12336730957031</v>
+        <v>-73.49198913574219</v>
       </c>
     </row>
     <row r="253">
@@ -4479,7 +4479,7 @@
         <v>4</v>
       </c>
       <c r="D253" t="n">
-        <v>-285.5059204101562</v>
+        <v>-281.7724304199219</v>
       </c>
     </row>
     <row r="254">
@@ -4495,7 +4495,7 @@
         <v>4</v>
       </c>
       <c r="D254" t="n">
-        <v>-270.9273376464844</v>
+        <v>-266.6674194335938</v>
       </c>
     </row>
     <row r="255">
@@ -4511,7 +4511,7 @@
         <v>2</v>
       </c>
       <c r="D255" t="n">
-        <v>-150.4843292236328</v>
+        <v>-147.5298461914062</v>
       </c>
     </row>
     <row r="256">
@@ -4527,7 +4527,7 @@
         <v>1</v>
       </c>
       <c r="D256" t="n">
-        <v>-78.29774475097656</v>
+        <v>-86.489013671875</v>
       </c>
     </row>
     <row r="257">
@@ -4543,7 +4543,7 @@
         <v>1</v>
       </c>
       <c r="D257" t="n">
-        <v>-84.81845092773438</v>
+        <v>-87.83348083496094</v>
       </c>
     </row>
     <row r="258">
@@ -4559,7 +4559,7 @@
         <v>1</v>
       </c>
       <c r="D258" t="n">
-        <v>-86.90357971191406</v>
+        <v>-90.6356201171875</v>
       </c>
     </row>
     <row r="259">
@@ -4575,7 +4575,7 @@
         <v>1</v>
       </c>
       <c r="D259" t="n">
-        <v>-73.67677307128906</v>
+        <v>-80.94471740722656</v>
       </c>
     </row>
     <row r="260">
@@ -4591,7 +4591,7 @@
         <v>4</v>
       </c>
       <c r="D260" t="n">
-        <v>-275.7984619140625</v>
+        <v>-282.1936645507812</v>
       </c>
     </row>
     <row r="261">
@@ -4607,7 +4607,7 @@
         <v>2</v>
       </c>
       <c r="D261" t="n">
-        <v>-150.6852111816406</v>
+        <v>-151.3356170654297</v>
       </c>
     </row>
     <row r="262">
@@ -4623,7 +4623,7 @@
         <v>2</v>
       </c>
       <c r="D262" t="n">
-        <v>-134.3783569335938</v>
+        <v>-135.5974731445312</v>
       </c>
     </row>
     <row r="263">
@@ -4639,7 +4639,7 @@
         <v>2</v>
       </c>
       <c r="D263" t="n">
-        <v>-159.2069702148438</v>
+        <v>-156.1833343505859</v>
       </c>
     </row>
     <row r="264">
@@ -4655,7 +4655,7 @@
         <v>2</v>
       </c>
       <c r="D264" t="n">
-        <v>-139.1592712402344</v>
+        <v>-143.1311187744141</v>
       </c>
     </row>
     <row r="265">
@@ -4671,7 +4671,7 @@
         <v>2</v>
       </c>
       <c r="D265" t="n">
-        <v>-141.1867370605469</v>
+        <v>-145.8213806152344</v>
       </c>
     </row>
     <row r="266">
@@ -4687,7 +4687,7 @@
         <v>1</v>
       </c>
       <c r="D266" t="n">
-        <v>-81.99034881591797</v>
+        <v>-82.27571868896484</v>
       </c>
     </row>
     <row r="267">
@@ -4703,7 +4703,7 @@
         <v>4</v>
       </c>
       <c r="D267" t="n">
-        <v>-233.8041839599609</v>
+        <v>-232.36474609375</v>
       </c>
     </row>
     <row r="268">
@@ -4719,7 +4719,7 @@
         <v>2</v>
       </c>
       <c r="D268" t="n">
-        <v>-135.9068145751953</v>
+        <v>-141.3659515380859</v>
       </c>
     </row>
     <row r="269">
@@ -4735,7 +4735,7 @@
         <v>4</v>
       </c>
       <c r="D269" t="n">
-        <v>-275.9966430664062</v>
+        <v>-283.5233154296875</v>
       </c>
     </row>
     <row r="270">
@@ -4751,7 +4751,7 @@
         <v>2</v>
       </c>
       <c r="D270" t="n">
-        <v>-164.0512542724609</v>
+        <v>-160.0604705810547</v>
       </c>
     </row>
     <row r="271">
@@ -4767,7 +4767,7 @@
         <v>2</v>
       </c>
       <c r="D271" t="n">
-        <v>-164.1138763427734</v>
+        <v>-160.4057159423828</v>
       </c>
     </row>
     <row r="272">
@@ -4783,7 +4783,7 @@
         <v>2</v>
       </c>
       <c r="D272" t="n">
-        <v>-145.1838989257812</v>
+        <v>-144.7125091552734</v>
       </c>
     </row>
     <row r="273">
@@ -4799,7 +4799,7 @@
         <v>4</v>
       </c>
       <c r="D273" t="n">
-        <v>-300.2225646972656</v>
+        <v>-299.4589233398438</v>
       </c>
     </row>
     <row r="274">
@@ -4815,7 +4815,7 @@
         <v>4</v>
       </c>
       <c r="D274" t="n">
-        <v>-305.1174621582031</v>
+        <v>-305.8491821289062</v>
       </c>
     </row>
     <row r="275">
@@ -4831,7 +4831,7 @@
         <v>4</v>
       </c>
       <c r="D275" t="n">
-        <v>-305.88037109375</v>
+        <v>-297.4778137207031</v>
       </c>
     </row>
     <row r="276">
@@ -4847,7 +4847,7 @@
         <v>2</v>
       </c>
       <c r="D276" t="n">
-        <v>-149.2087097167969</v>
+        <v>-150.7125854492188</v>
       </c>
     </row>
     <row r="277">
@@ -4863,7 +4863,7 @@
         <v>2</v>
       </c>
       <c r="D277" t="n">
-        <v>-151.111572265625</v>
+        <v>-152.8955688476562</v>
       </c>
     </row>
     <row r="278">
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="D278" t="n">
-        <v>-288.6643981933594</v>
+        <v>-295.0179138183594</v>
       </c>
     </row>
     <row r="279">
@@ -4895,7 +4895,7 @@
         <v>2</v>
       </c>
       <c r="D279" t="n">
-        <v>-132.7259216308594</v>
+        <v>-134.8380126953125</v>
       </c>
     </row>
     <row r="280">
@@ -4911,7 +4911,7 @@
         <v>2</v>
       </c>
       <c r="D280" t="n">
-        <v>-161.2083892822266</v>
+        <v>-159.0217132568359</v>
       </c>
     </row>
     <row r="281">
@@ -4927,7 +4927,7 @@
         <v>2</v>
       </c>
       <c r="D281" t="n">
-        <v>-138.7018280029297</v>
+        <v>-137.7362670898438</v>
       </c>
     </row>
     <row r="282">
@@ -4943,7 +4943,7 @@
         <v>2</v>
       </c>
       <c r="D282" t="n">
-        <v>-172.2877044677734</v>
+        <v>-169.0542297363281</v>
       </c>
     </row>
     <row r="283">
@@ -4959,7 +4959,7 @@
         <v>4</v>
       </c>
       <c r="D283" t="n">
-        <v>-293.8302612304688</v>
+        <v>-285.314453125</v>
       </c>
     </row>
     <row r="284">
@@ -4975,7 +4975,7 @@
         <v>2</v>
       </c>
       <c r="D284" t="n">
-        <v>-166.3559417724609</v>
+        <v>-164.6370849609375</v>
       </c>
     </row>
     <row r="285">
@@ -4991,7 +4991,7 @@
         <v>2</v>
       </c>
       <c r="D285" t="n">
-        <v>-150.2129974365234</v>
+        <v>-155.3954467773438</v>
       </c>
     </row>
     <row r="286">
@@ -5007,7 +5007,7 @@
         <v>2</v>
       </c>
       <c r="D286" t="n">
-        <v>-153.5739440917969</v>
+        <v>-156.4569091796875</v>
       </c>
     </row>
     <row r="287">
@@ -5023,7 +5023,7 @@
         <v>4</v>
       </c>
       <c r="D287" t="n">
-        <v>-261.7547607421875</v>
+        <v>-260.8756103515625</v>
       </c>
     </row>
     <row r="288">
@@ -5039,7 +5039,7 @@
         <v>2</v>
       </c>
       <c r="D288" t="n">
-        <v>-143.3932495117188</v>
+        <v>-144.0422821044922</v>
       </c>
     </row>
     <row r="289">
@@ -5055,7 +5055,7 @@
         <v>2</v>
       </c>
       <c r="D289" t="n">
-        <v>-155.8287048339844</v>
+        <v>-150.1921081542969</v>
       </c>
     </row>
     <row r="290">
@@ -5071,7 +5071,7 @@
         <v>2</v>
       </c>
       <c r="D290" t="n">
-        <v>-144.7101135253906</v>
+        <v>-147.0261688232422</v>
       </c>
     </row>
     <row r="291">
@@ -5087,7 +5087,7 @@
         <v>2</v>
       </c>
       <c r="D291" t="n">
-        <v>-132.6480865478516</v>
+        <v>-138.6236114501953</v>
       </c>
     </row>
   </sheetData>

--- a/dps_params.xlsx
+++ b/dps_params.xlsx
@@ -460,10 +460,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D2" t="n">
-        <v>-312.7757873535156</v>
+        <v>-312.7254333496094</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +476,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D3" t="n">
-        <v>-131.5140838623047</v>
+        <v>-131.4637298583984</v>
       </c>
     </row>
     <row r="4">
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D4" t="n">
-        <v>-75.88648986816406</v>
+        <v>-75.83651733398438</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D5" t="n">
-        <v>-94.108154296875</v>
+        <v>-94.05818176269531</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D6" t="n">
-        <v>-280.8714599609375</v>
+        <v>-280.8211059570312</v>
       </c>
     </row>
     <row r="7">
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D7" t="n">
-        <v>-85.23464202880859</v>
+        <v>-85.18466949462891</v>
       </c>
     </row>
     <row r="8">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D8" t="n">
-        <v>-67.84782409667969</v>
+        <v>-67.7978515625</v>
       </c>
     </row>
     <row r="9">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D9" t="n">
-        <v>-77.71986389160156</v>
+        <v>-77.66989135742188</v>
       </c>
     </row>
     <row r="10">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D10" t="n">
-        <v>-70.32724761962891</v>
+        <v>-70.27727508544922</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D11" t="n">
-        <v>-75.32581329345703</v>
+        <v>-75.27584075927734</v>
       </c>
     </row>
     <row r="12">
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D12" t="n">
-        <v>-236.6942291259766</v>
+        <v>-236.6438751220703</v>
       </c>
     </row>
     <row r="13">
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D13" t="n">
-        <v>-79.01725006103516</v>
+        <v>-78.96727752685547</v>
       </c>
     </row>
     <row r="14">
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D14" t="n">
-        <v>-162.1633453369141</v>
+        <v>-162.1129913330078</v>
       </c>
     </row>
     <row r="15">
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D15" t="n">
-        <v>-82.53616333007812</v>
+        <v>-82.48619079589844</v>
       </c>
     </row>
     <row r="16">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D16" t="n">
-        <v>-76.85581970214844</v>
+        <v>-76.80584716796875</v>
       </c>
     </row>
     <row r="17">
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D17" t="n">
-        <v>-141.9286651611328</v>
+        <v>-141.8783111572266</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D18" t="n">
-        <v>-172.1657104492188</v>
+        <v>-172.1153564453125</v>
       </c>
     </row>
     <row r="19">
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D19" t="n">
-        <v>-85.7677001953125</v>
+        <v>-85.71772766113281</v>
       </c>
     </row>
     <row r="20">
@@ -748,10 +748,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D20" t="n">
-        <v>-133.7468719482422</v>
+        <v>-133.6965179443359</v>
       </c>
     </row>
     <row r="21">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D21" t="n">
-        <v>-75.62960815429688</v>
+        <v>-75.57963562011719</v>
       </c>
     </row>
     <row r="22">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D22" t="n">
-        <v>-153.9105224609375</v>
+        <v>-153.8601684570312</v>
       </c>
     </row>
     <row r="23">
@@ -796,10 +796,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D23" t="n">
-        <v>-80.67966461181641</v>
+        <v>-80.62969207763672</v>
       </c>
     </row>
     <row r="24">
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D24" t="n">
-        <v>-84.42353820800781</v>
+        <v>-84.37356567382812</v>
       </c>
     </row>
     <row r="25">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D25" t="n">
-        <v>-82.71511077880859</v>
+        <v>-82.66513824462891</v>
       </c>
     </row>
     <row r="26">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D26" t="n">
-        <v>-81.03924560546875</v>
+        <v>-80.98927307128906</v>
       </c>
     </row>
     <row r="27">
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D27" t="n">
-        <v>-304.7581787109375</v>
+        <v>-304.7078247070312</v>
       </c>
     </row>
     <row r="28">
@@ -876,10 +876,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D28" t="n">
-        <v>-160.8372344970703</v>
+        <v>-160.7868804931641</v>
       </c>
     </row>
     <row r="29">
@@ -892,10 +892,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D29" t="n">
-        <v>-283.3493041992188</v>
+        <v>-283.2989501953125</v>
       </c>
     </row>
     <row r="30">
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D30" t="n">
-        <v>-293.1230773925781</v>
+        <v>-293.0727233886719</v>
       </c>
     </row>
     <row r="31">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D31" t="n">
-        <v>-87.68689727783203</v>
+        <v>-87.63692474365234</v>
       </c>
     </row>
     <row r="32">
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D32" t="n">
-        <v>-66.42996215820312</v>
+        <v>-66.37998962402344</v>
       </c>
     </row>
     <row r="33">
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D33" t="n">
-        <v>-238.8040161132812</v>
+        <v>-238.753662109375</v>
       </c>
     </row>
     <row r="34">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D34" t="n">
-        <v>-273.1069030761719</v>
+        <v>-273.0565490722656</v>
       </c>
     </row>
     <row r="35">
@@ -988,10 +988,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D35" t="n">
-        <v>-86.92874145507812</v>
+        <v>-86.87876892089844</v>
       </c>
     </row>
     <row r="36">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D36" t="n">
-        <v>-79.61103820800781</v>
+        <v>-79.56106567382812</v>
       </c>
     </row>
     <row r="37">
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D37" t="n">
-        <v>-147.7962493896484</v>
+        <v>-147.7458953857422</v>
       </c>
     </row>
     <row r="38">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D38" t="n">
-        <v>-139.0652770996094</v>
+        <v>-139.0149230957031</v>
       </c>
     </row>
     <row r="39">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D39" t="n">
-        <v>-80.14743041992188</v>
+        <v>-80.09745788574219</v>
       </c>
     </row>
     <row r="40">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D40" t="n">
-        <v>-143.899169921875</v>
+        <v>-143.8488159179688</v>
       </c>
     </row>
     <row r="41">
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D41" t="n">
-        <v>-137.2330780029297</v>
+        <v>-137.1827239990234</v>
       </c>
     </row>
     <row r="42">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D42" t="n">
-        <v>-89.46537780761719</v>
+        <v>-89.4154052734375</v>
       </c>
     </row>
     <row r="43">
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D43" t="n">
-        <v>-78.8984375</v>
+        <v>-78.84846496582031</v>
       </c>
     </row>
     <row r="44">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D44" t="n">
-        <v>-149.2513885498047</v>
+        <v>-149.2010345458984</v>
       </c>
     </row>
     <row r="45">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D45" t="n">
-        <v>-79.52750396728516</v>
+        <v>-79.47753143310547</v>
       </c>
     </row>
     <row r="46">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D46" t="n">
-        <v>-301.6453857421875</v>
+        <v>-301.5950317382812</v>
       </c>
     </row>
     <row r="47">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D47" t="n">
-        <v>-80.38056182861328</v>
+        <v>-80.33058929443359</v>
       </c>
     </row>
     <row r="48">
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D48" t="n">
-        <v>-251.2189788818359</v>
+        <v>-251.1686248779297</v>
       </c>
     </row>
     <row r="49">
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D49" t="n">
-        <v>-222.1041107177734</v>
+        <v>-222.0537567138672</v>
       </c>
     </row>
     <row r="50">
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D50" t="n">
-        <v>-140.1507568359375</v>
+        <v>-140.1004028320312</v>
       </c>
     </row>
     <row r="51">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D51" t="n">
-        <v>-79.82917022705078</v>
+        <v>-79.77919769287109</v>
       </c>
     </row>
     <row r="52">
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D52" t="n">
-        <v>-146.8721313476562</v>
+        <v>-146.82177734375</v>
       </c>
     </row>
     <row r="53">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D53" t="n">
-        <v>-83.03791809082031</v>
+        <v>-82.98794555664062</v>
       </c>
     </row>
     <row r="54">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D54" t="n">
-        <v>-88.17540740966797</v>
+        <v>-88.12543487548828</v>
       </c>
     </row>
     <row r="55">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D55" t="n">
-        <v>-170.7767181396484</v>
+        <v>-170.7263641357422</v>
       </c>
     </row>
     <row r="56">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D56" t="n">
-        <v>-140.1629943847656</v>
+        <v>-140.1126403808594</v>
       </c>
     </row>
     <row r="57">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D57" t="n">
-        <v>-79.80036163330078</v>
+        <v>-79.75038909912109</v>
       </c>
     </row>
     <row r="58">
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D58" t="n">
-        <v>-242.427001953125</v>
+        <v>-242.3766479492188</v>
       </c>
     </row>
     <row r="59">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D59" t="n">
-        <v>-127.6919860839844</v>
+        <v>-127.6420135498047</v>
       </c>
     </row>
     <row r="60">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D60" t="n">
-        <v>-258.9580078125</v>
+        <v>-258.9076538085938</v>
       </c>
     </row>
     <row r="61">
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D61" t="n">
-        <v>-172.2892150878906</v>
+        <v>-172.2388610839844</v>
       </c>
     </row>
     <row r="62">
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D62" t="n">
-        <v>-85.5037841796875</v>
+        <v>-85.45381164550781</v>
       </c>
     </row>
     <row r="63">
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D63" t="n">
-        <v>-118.6301956176758</v>
+        <v>-118.5802230834961</v>
       </c>
     </row>
     <row r="64">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D64" t="n">
-        <v>-83.99555206298828</v>
+        <v>-83.94557952880859</v>
       </c>
     </row>
     <row r="65">
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D65" t="n">
-        <v>-168.9671173095703</v>
+        <v>-168.9167633056641</v>
       </c>
     </row>
     <row r="66">
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D66" t="n">
-        <v>-128.9008483886719</v>
+        <v>-128.8504943847656</v>
       </c>
     </row>
     <row r="67">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D67" t="n">
-        <v>-140.9709320068359</v>
+        <v>-140.9205780029297</v>
       </c>
     </row>
     <row r="68">
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D68" t="n">
-        <v>-78.59947967529297</v>
+        <v>-78.54950714111328</v>
       </c>
     </row>
     <row r="69">
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D69" t="n">
-        <v>-139.8025665283203</v>
+        <v>-139.7522125244141</v>
       </c>
     </row>
     <row r="70">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D70" t="n">
-        <v>-76.41378784179688</v>
+        <v>-76.36381530761719</v>
       </c>
     </row>
     <row r="71">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D71" t="n">
-        <v>-81.67057037353516</v>
+        <v>-81.62059783935547</v>
       </c>
     </row>
     <row r="72">
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D72" t="n">
-        <v>-328.6674499511719</v>
+        <v>-328.6170959472656</v>
       </c>
     </row>
     <row r="73">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D73" t="n">
-        <v>-134.2458648681641</v>
+        <v>-134.1955108642578</v>
       </c>
     </row>
     <row r="74">
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D74" t="n">
-        <v>-74.20224761962891</v>
+        <v>-74.15227508544922</v>
       </c>
     </row>
     <row r="75">
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D75" t="n">
-        <v>-118.1796340942383</v>
+        <v>-118.1296615600586</v>
       </c>
     </row>
     <row r="76">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D76" t="n">
-        <v>-123.8785781860352</v>
+        <v>-123.8286056518555</v>
       </c>
     </row>
     <row r="77">
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D77" t="n">
-        <v>-247.5622711181641</v>
+        <v>-247.5119171142578</v>
       </c>
     </row>
     <row r="78">
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D78" t="n">
-        <v>-154.4074554443359</v>
+        <v>-154.3571014404297</v>
       </c>
     </row>
     <row r="79">
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D79" t="n">
-        <v>-146.2172393798828</v>
+        <v>-146.1668853759766</v>
       </c>
     </row>
     <row r="80">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D80" t="n">
-        <v>-159.734130859375</v>
+        <v>-159.6837768554688</v>
       </c>
     </row>
     <row r="81">
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D81" t="n">
-        <v>-217.0181427001953</v>
+        <v>-216.9677886962891</v>
       </c>
     </row>
     <row r="82">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D82" t="n">
-        <v>-153.9062652587891</v>
+        <v>-153.8559112548828</v>
       </c>
     </row>
     <row r="83">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D83" t="n">
-        <v>-321.4641723632812</v>
+        <v>-321.413818359375</v>
       </c>
     </row>
     <row r="84">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D84" t="n">
-        <v>-89.32257843017578</v>
+        <v>-89.27260589599609</v>
       </c>
     </row>
     <row r="85">
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D85" t="n">
-        <v>-141.1580200195312</v>
+        <v>-141.107666015625</v>
       </c>
     </row>
     <row r="86">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D86" t="n">
-        <v>-76.47366333007812</v>
+        <v>-76.42369079589844</v>
       </c>
     </row>
     <row r="87">
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D87" t="n">
-        <v>-126.2312545776367</v>
+        <v>-126.181282043457</v>
       </c>
     </row>
     <row r="88">
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D88" t="n">
-        <v>-146.6411437988281</v>
+        <v>-146.5907897949219</v>
       </c>
     </row>
     <row r="89">
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D89" t="n">
-        <v>-281.5845031738281</v>
+        <v>-281.5341491699219</v>
       </c>
     </row>
     <row r="90">
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D90" t="n">
-        <v>-158.1317291259766</v>
+        <v>-158.0813751220703</v>
       </c>
     </row>
     <row r="91">
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D91" t="n">
-        <v>-83.46322631835938</v>
+        <v>-83.41325378417969</v>
       </c>
     </row>
     <row r="92">
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D92" t="n">
-        <v>-142.9967346191406</v>
+        <v>-142.9463806152344</v>
       </c>
     </row>
     <row r="93">
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D93" t="n">
-        <v>-136.2752685546875</v>
+        <v>-136.2249145507812</v>
       </c>
     </row>
     <row r="94">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D94" t="n">
-        <v>-287.8291931152344</v>
+        <v>-287.7788391113281</v>
       </c>
     </row>
     <row r="95">
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D95" t="n">
-        <v>-133.0659637451172</v>
+        <v>-133.0156097412109</v>
       </c>
     </row>
     <row r="96">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D96" t="n">
-        <v>-137.7978210449219</v>
+        <v>-137.7474670410156</v>
       </c>
     </row>
     <row r="97">
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D97" t="n">
-        <v>-77.16901397705078</v>
+        <v>-77.11904144287109</v>
       </c>
     </row>
     <row r="98">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D98" t="n">
-        <v>-142.02197265625</v>
+        <v>-141.9716186523438</v>
       </c>
     </row>
     <row r="99">
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D99" t="n">
-        <v>-152.9811248779297</v>
+        <v>-152.9307708740234</v>
       </c>
     </row>
     <row r="100">
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D100" t="n">
-        <v>-165.0660858154297</v>
+        <v>-165.0157318115234</v>
       </c>
     </row>
     <row r="101">
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D101" t="n">
-        <v>-268.0858764648438</v>
+        <v>-268.0355224609375</v>
       </c>
     </row>
     <row r="102">
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D102" t="n">
-        <v>-84.41999816894531</v>
+        <v>-84.37002563476562</v>
       </c>
     </row>
     <row r="103">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D103" t="n">
-        <v>-114.7257080078125</v>
+        <v>-114.6757354736328</v>
       </c>
     </row>
     <row r="104">
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D104" t="n">
-        <v>-83.75466156005859</v>
+        <v>-83.70468902587891</v>
       </c>
     </row>
     <row r="105">
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D105" t="n">
-        <v>-156.8981170654297</v>
+        <v>-156.8477630615234</v>
       </c>
     </row>
     <row r="106">
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D106" t="n">
-        <v>-120.8911209106445</v>
+        <v>-120.8411483764648</v>
       </c>
     </row>
     <row r="107">
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D107" t="n">
-        <v>-155.3239898681641</v>
+        <v>-155.2736358642578</v>
       </c>
     </row>
     <row r="108">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D108" t="n">
-        <v>-303.7877502441406</v>
+        <v>-303.7373962402344</v>
       </c>
     </row>
     <row r="109">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D109" t="n">
-        <v>-125.7340393066406</v>
+        <v>-125.6840667724609</v>
       </c>
     </row>
     <row r="110">
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D110" t="n">
-        <v>-89.494384765625</v>
+        <v>-89.44441223144531</v>
       </c>
     </row>
     <row r="111">
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D111" t="n">
-        <v>-80.56299591064453</v>
+        <v>-80.51302337646484</v>
       </c>
     </row>
     <row r="112">
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D112" t="n">
-        <v>-124.9062347412109</v>
+        <v>-124.8562622070312</v>
       </c>
     </row>
     <row r="113">
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D113" t="n">
-        <v>-166.9066925048828</v>
+        <v>-166.8563385009766</v>
       </c>
     </row>
     <row r="114">
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D114" t="n">
-        <v>-84.74359893798828</v>
+        <v>-84.69362640380859</v>
       </c>
     </row>
     <row r="115">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D115" t="n">
-        <v>-313.0737609863281</v>
+        <v>-313.0234069824219</v>
       </c>
     </row>
     <row r="116">
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D116" t="n">
-        <v>-83.99855041503906</v>
+        <v>-83.94857788085938</v>
       </c>
     </row>
     <row r="117">
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D117" t="n">
-        <v>-328.6477966308594</v>
+        <v>-328.5974426269531</v>
       </c>
     </row>
     <row r="118">
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D118" t="n">
-        <v>-76.95477294921875</v>
+        <v>-76.90480041503906</v>
       </c>
     </row>
     <row r="119">
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D119" t="n">
-        <v>-295.3050537109375</v>
+        <v>-295.2546997070312</v>
       </c>
     </row>
     <row r="120">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D120" t="n">
-        <v>-153.3857269287109</v>
+        <v>-153.3353729248047</v>
       </c>
     </row>
     <row r="121">
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D121" t="n">
-        <v>-82.38832855224609</v>
+        <v>-82.33835601806641</v>
       </c>
     </row>
     <row r="122">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D122" t="n">
-        <v>-164.2074432373047</v>
+        <v>-164.1570892333984</v>
       </c>
     </row>
     <row r="123">
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D123" t="n">
-        <v>-76.27633666992188</v>
+        <v>-76.22636413574219</v>
       </c>
     </row>
     <row r="124">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D124" t="n">
-        <v>-76.79575347900391</v>
+        <v>-76.74578094482422</v>
       </c>
     </row>
     <row r="125">
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D125" t="n">
-        <v>-149.9316558837891</v>
+        <v>-149.8813018798828</v>
       </c>
     </row>
     <row r="126">
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D126" t="n">
-        <v>-160.6572723388672</v>
+        <v>-160.6069183349609</v>
       </c>
     </row>
     <row r="127">
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D127" t="n">
-        <v>-111.4554901123047</v>
+        <v>-111.405517578125</v>
       </c>
     </row>
     <row r="128">
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D128" t="n">
-        <v>-159.4218292236328</v>
+        <v>-159.3714752197266</v>
       </c>
     </row>
     <row r="129">
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D129" t="n">
-        <v>-320.92041015625</v>
+        <v>-320.8700561523438</v>
       </c>
     </row>
     <row r="130">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D130" t="n">
-        <v>-74.76960754394531</v>
+        <v>-74.71963500976562</v>
       </c>
     </row>
     <row r="131">
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D131" t="n">
-        <v>-79.46607208251953</v>
+        <v>-79.41609954833984</v>
       </c>
     </row>
     <row r="132">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D132" t="n">
-        <v>-77.08785247802734</v>
+        <v>-77.03787994384766</v>
       </c>
     </row>
     <row r="133">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D133" t="n">
-        <v>-82.26343536376953</v>
+        <v>-82.21346282958984</v>
       </c>
     </row>
     <row r="134">
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D134" t="n">
-        <v>-65.56641387939453</v>
+        <v>-65.51644134521484</v>
       </c>
     </row>
     <row r="135">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D135" t="n">
-        <v>-287.2226257324219</v>
+        <v>-287.1722717285156</v>
       </c>
     </row>
     <row r="136">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D136" t="n">
-        <v>-279.2212219238281</v>
+        <v>-279.1708679199219</v>
       </c>
     </row>
     <row r="137">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D137" t="n">
-        <v>-146.6395568847656</v>
+        <v>-146.5892028808594</v>
       </c>
     </row>
     <row r="138">
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D138" t="n">
-        <v>-76.14176177978516</v>
+        <v>-76.09178924560547</v>
       </c>
     </row>
     <row r="139">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D139" t="n">
-        <v>-283.7652893066406</v>
+        <v>-283.7149353027344</v>
       </c>
     </row>
     <row r="140">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D140" t="n">
-        <v>-112.6419372558594</v>
+        <v>-112.5919647216797</v>
       </c>
     </row>
     <row r="141">
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D141" t="n">
-        <v>-88.72606658935547</v>
+        <v>-88.67609405517578</v>
       </c>
     </row>
     <row r="142">
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D142" t="n">
-        <v>-154.3799133300781</v>
+        <v>-154.3295593261719</v>
       </c>
     </row>
     <row r="143">
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D143" t="n">
-        <v>-141.1440124511719</v>
+        <v>-141.0936584472656</v>
       </c>
     </row>
     <row r="144">
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D144" t="n">
-        <v>-271.1011047363281</v>
+        <v>-271.0507507324219</v>
       </c>
     </row>
     <row r="145">
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D145" t="n">
-        <v>-122.1092147827148</v>
+        <v>-122.0592422485352</v>
       </c>
     </row>
     <row r="146">
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D146" t="n">
-        <v>-76.92984008789062</v>
+        <v>-76.87986755371094</v>
       </c>
     </row>
     <row r="147">
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D147" t="n">
-        <v>-166.9119720458984</v>
+        <v>-166.8616180419922</v>
       </c>
     </row>
     <row r="148">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D148" t="n">
-        <v>-77.52755737304688</v>
+        <v>-77.47758483886719</v>
       </c>
     </row>
     <row r="149">
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D149" t="n">
-        <v>-262.2939453125</v>
+        <v>-262.2435913085938</v>
       </c>
     </row>
     <row r="150">
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D150" t="n">
-        <v>-157.6202087402344</v>
+        <v>-157.5698547363281</v>
       </c>
     </row>
     <row r="151">
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D151" t="n">
-        <v>-129.8075714111328</v>
+        <v>-129.7572174072266</v>
       </c>
     </row>
     <row r="152">
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D152" t="n">
-        <v>-83.51857757568359</v>
+        <v>-83.46860504150391</v>
       </c>
     </row>
     <row r="153">
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D153" t="n">
-        <v>-136.2218322753906</v>
+        <v>-136.1714782714844</v>
       </c>
     </row>
     <row r="154">
@@ -2892,10 +2892,10 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D154" t="n">
-        <v>-81.11664581298828</v>
+        <v>-81.06667327880859</v>
       </c>
     </row>
     <row r="155">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D155" t="n">
-        <v>-124.919677734375</v>
+        <v>-124.8697052001953</v>
       </c>
     </row>
     <row r="156">
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D156" t="n">
-        <v>-150.9056243896484</v>
+        <v>-150.8552703857422</v>
       </c>
     </row>
     <row r="157">
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D157" t="n">
-        <v>-166.4950256347656</v>
+        <v>-166.4446716308594</v>
       </c>
     </row>
     <row r="158">
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D158" t="n">
-        <v>-221.5299682617188</v>
+        <v>-221.4796142578125</v>
       </c>
     </row>
     <row r="159">
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D159" t="n">
-        <v>-161.8446197509766</v>
+        <v>-161.7942657470703</v>
       </c>
     </row>
     <row r="160">
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D160" t="n">
-        <v>-77.48191833496094</v>
+        <v>-77.43194580078125</v>
       </c>
     </row>
     <row r="161">
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D161" t="n">
-        <v>-165.3515625</v>
+        <v>-165.3012084960938</v>
       </c>
     </row>
     <row r="162">
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D162" t="n">
-        <v>-168.0431976318359</v>
+        <v>-167.9928436279297</v>
       </c>
     </row>
     <row r="163">
@@ -3036,10 +3036,10 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D163" t="n">
-        <v>-78.96121215820312</v>
+        <v>-78.91123962402344</v>
       </c>
     </row>
     <row r="164">
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D164" t="n">
-        <v>-140.8423309326172</v>
+        <v>-140.7919769287109</v>
       </c>
     </row>
     <row r="165">
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D165" t="n">
-        <v>-142.3974761962891</v>
+        <v>-142.3471221923828</v>
       </c>
     </row>
     <row r="166">
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D166" t="n">
-        <v>-123.1963348388672</v>
+        <v>-123.1463623046875</v>
       </c>
     </row>
     <row r="167">
@@ -3100,10 +3100,10 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D167" t="n">
-        <v>-68.05825805664062</v>
+        <v>-68.00828552246094</v>
       </c>
     </row>
     <row r="168">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D168" t="n">
-        <v>-150.4101257324219</v>
+        <v>-150.3597717285156</v>
       </c>
     </row>
     <row r="169">
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D169" t="n">
-        <v>-72.12531280517578</v>
+        <v>-72.07534027099609</v>
       </c>
     </row>
     <row r="170">
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D170" t="n">
-        <v>-81.53610992431641</v>
+        <v>-81.48613739013672</v>
       </c>
     </row>
     <row r="171">
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D171" t="n">
-        <v>-94.9534912109375</v>
+        <v>-94.90351867675781</v>
       </c>
     </row>
     <row r="172">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D172" t="n">
-        <v>-81.673095703125</v>
+        <v>-81.62312316894531</v>
       </c>
     </row>
     <row r="173">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D173" t="n">
-        <v>-311.0089111328125</v>
+        <v>-310.9585571289062</v>
       </c>
     </row>
     <row r="174">
@@ -3212,10 +3212,10 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D174" t="n">
-        <v>-83.23433685302734</v>
+        <v>-83.18436431884766</v>
       </c>
     </row>
     <row r="175">
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D175" t="n">
-        <v>-159.924560546875</v>
+        <v>-159.8742065429688</v>
       </c>
     </row>
     <row r="176">
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D176" t="n">
-        <v>-291.809326171875</v>
+        <v>-291.7589721679688</v>
       </c>
     </row>
     <row r="177">
@@ -3260,10 +3260,10 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D177" t="n">
-        <v>-132.9282379150391</v>
+        <v>-132.8778839111328</v>
       </c>
     </row>
     <row r="178">
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D178" t="n">
-        <v>-156.6605529785156</v>
+        <v>-156.6101989746094</v>
       </c>
     </row>
     <row r="179">
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D179" t="n">
-        <v>-304.3961791992188</v>
+        <v>-304.3458251953125</v>
       </c>
     </row>
     <row r="180">
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D180" t="n">
-        <v>-156.9090881347656</v>
+        <v>-156.8587341308594</v>
       </c>
     </row>
     <row r="181">
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D181" t="n">
-        <v>-83.38128662109375</v>
+        <v>-83.33131408691406</v>
       </c>
     </row>
     <row r="182">
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D182" t="n">
-        <v>-130.5007476806641</v>
+        <v>-130.4503936767578</v>
       </c>
     </row>
     <row r="183">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D183" t="n">
-        <v>-79.68167114257812</v>
+        <v>-79.63169860839844</v>
       </c>
     </row>
     <row r="184">
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D184" t="n">
-        <v>-223.1823577880859</v>
+        <v>-223.1320037841797</v>
       </c>
     </row>
     <row r="185">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D185" t="n">
-        <v>-164.4349670410156</v>
+        <v>-164.3846130371094</v>
       </c>
     </row>
     <row r="186">
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D186" t="n">
-        <v>-147.9378051757812</v>
+        <v>-147.887451171875</v>
       </c>
     </row>
     <row r="187">
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D187" t="n">
-        <v>-159.9310913085938</v>
+        <v>-159.8807373046875</v>
       </c>
     </row>
     <row r="188">
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D188" t="n">
-        <v>-144.5268249511719</v>
+        <v>-144.4764709472656</v>
       </c>
     </row>
     <row r="189">
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D189" t="n">
-        <v>-72.51679992675781</v>
+        <v>-72.46682739257812</v>
       </c>
     </row>
     <row r="190">
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D190" t="n">
-        <v>-263.9480590820312</v>
+        <v>-263.897705078125</v>
       </c>
     </row>
     <row r="191">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D191" t="n">
-        <v>-124.8707122802734</v>
+        <v>-124.8207397460938</v>
       </c>
     </row>
     <row r="192">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D192" t="n">
-        <v>-76.755615234375</v>
+        <v>-76.70564270019531</v>
       </c>
     </row>
     <row r="193">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D193" t="n">
-        <v>-82.04090881347656</v>
+        <v>-81.99093627929688</v>
       </c>
     </row>
     <row r="194">
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D194" t="n">
-        <v>-155.453125</v>
+        <v>-155.4027709960938</v>
       </c>
     </row>
     <row r="195">
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D195" t="n">
-        <v>-303.3656005859375</v>
+        <v>-303.3152465820312</v>
       </c>
     </row>
     <row r="196">
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D196" t="n">
-        <v>-320.0258483886719</v>
+        <v>-319.9754943847656</v>
       </c>
     </row>
     <row r="197">
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D197" t="n">
-        <v>-77.80377960205078</v>
+        <v>-77.75380706787109</v>
       </c>
     </row>
     <row r="198">
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D198" t="n">
-        <v>-155.2765502929688</v>
+        <v>-155.2261962890625</v>
       </c>
     </row>
     <row r="199">
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D199" t="n">
-        <v>-128.7712554931641</v>
+        <v>-128.7209014892578</v>
       </c>
     </row>
     <row r="200">
@@ -3628,10 +3628,10 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D200" t="n">
-        <v>-139.4909820556641</v>
+        <v>-139.4406280517578</v>
       </c>
     </row>
     <row r="201">
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D201" t="n">
-        <v>-321.418701171875</v>
+        <v>-321.3683471679688</v>
       </c>
     </row>
     <row r="202">
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D202" t="n">
-        <v>-155.5260467529297</v>
+        <v>-155.4756927490234</v>
       </c>
     </row>
     <row r="203">
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D203" t="n">
-        <v>-79.34042358398438</v>
+        <v>-79.29045104980469</v>
       </c>
     </row>
     <row r="204">
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D204" t="n">
-        <v>-297.3146667480469</v>
+        <v>-297.2643127441406</v>
       </c>
     </row>
     <row r="205">
@@ -3708,10 +3708,10 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D205" t="n">
-        <v>-82.83698272705078</v>
+        <v>-82.78701019287109</v>
       </c>
     </row>
     <row r="206">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D206" t="n">
-        <v>-78.80796813964844</v>
+        <v>-78.75799560546875</v>
       </c>
     </row>
     <row r="207">
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D207" t="n">
-        <v>-167.9123077392578</v>
+        <v>-167.8619537353516</v>
       </c>
     </row>
     <row r="208">
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D208" t="n">
-        <v>-128.9845123291016</v>
+        <v>-128.9341583251953</v>
       </c>
     </row>
     <row r="209">
@@ -3772,10 +3772,10 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D209" t="n">
-        <v>-126.9576950073242</v>
+        <v>-126.9077224731445</v>
       </c>
     </row>
     <row r="210">
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D210" t="n">
-        <v>-140.2644805908203</v>
+        <v>-140.2141265869141</v>
       </c>
     </row>
     <row r="211">
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D211" t="n">
-        <v>-109.3626327514648</v>
+        <v>-109.3126602172852</v>
       </c>
     </row>
     <row r="212">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D212" t="n">
-        <v>-86.53759002685547</v>
+        <v>-86.48761749267578</v>
       </c>
     </row>
     <row r="213">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D213" t="n">
-        <v>-73.15424346923828</v>
+        <v>-73.10427093505859</v>
       </c>
     </row>
     <row r="214">
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D214" t="n">
-        <v>-142.8046722412109</v>
+        <v>-142.7543182373047</v>
       </c>
     </row>
     <row r="215">
@@ -3868,10 +3868,10 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D215" t="n">
-        <v>-95.81846618652344</v>
+        <v>-95.76849365234375</v>
       </c>
     </row>
     <row r="216">
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D216" t="n">
-        <v>-148.0325469970703</v>
+        <v>-147.9821929931641</v>
       </c>
     </row>
     <row r="217">
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D217" t="n">
-        <v>-139.7101745605469</v>
+        <v>-139.6598205566406</v>
       </c>
     </row>
     <row r="218">
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D218" t="n">
-        <v>-148.0384216308594</v>
+        <v>-147.9880676269531</v>
       </c>
     </row>
     <row r="219">
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D219" t="n">
-        <v>-134.5567169189453</v>
+        <v>-134.5063629150391</v>
       </c>
     </row>
     <row r="220">
@@ -3948,10 +3948,10 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D220" t="n">
-        <v>-143.5973815917969</v>
+        <v>-143.5470275878906</v>
       </c>
     </row>
     <row r="221">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D221" t="n">
-        <v>-154.3467407226562</v>
+        <v>-154.29638671875</v>
       </c>
     </row>
     <row r="222">
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D222" t="n">
-        <v>-143.9088592529297</v>
+        <v>-143.8585052490234</v>
       </c>
     </row>
     <row r="223">
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D223" t="n">
-        <v>-93.99896240234375</v>
+        <v>-93.94898986816406</v>
       </c>
     </row>
     <row r="224">
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D224" t="n">
-        <v>-78.56758117675781</v>
+        <v>-78.51760864257812</v>
       </c>
     </row>
     <row r="225">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D225" t="n">
-        <v>-76.20285034179688</v>
+        <v>-76.15287780761719</v>
       </c>
     </row>
     <row r="226">
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D226" t="n">
-        <v>-144.0987701416016</v>
+        <v>-144.0484161376953</v>
       </c>
     </row>
     <row r="227">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D227" t="n">
-        <v>-87.01181030273438</v>
+        <v>-86.96183776855469</v>
       </c>
     </row>
     <row r="228">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D228" t="n">
-        <v>-147.2466430664062</v>
+        <v>-147.1962890625</v>
       </c>
     </row>
     <row r="229">
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D229" t="n">
-        <v>-89.93679809570312</v>
+        <v>-89.88682556152344</v>
       </c>
     </row>
     <row r="230">
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D230" t="n">
-        <v>-131.5619659423828</v>
+        <v>-131.5116119384766</v>
       </c>
     </row>
     <row r="231">
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D231" t="n">
-        <v>-161.1687316894531</v>
+        <v>-161.1183776855469</v>
       </c>
     </row>
     <row r="232">
@@ -4140,10 +4140,10 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D232" t="n">
-        <v>-137.1577758789062</v>
+        <v>-137.107421875</v>
       </c>
     </row>
     <row r="233">
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D233" t="n">
-        <v>-139.0460662841797</v>
+        <v>-138.9957122802734</v>
       </c>
     </row>
     <row r="234">
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D234" t="n">
-        <v>-329.5998840332031</v>
+        <v>-329.5495300292969</v>
       </c>
     </row>
     <row r="235">
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D235" t="n">
-        <v>-312.3600463867188</v>
+        <v>-312.3096923828125</v>
       </c>
     </row>
     <row r="236">
@@ -4204,10 +4204,10 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D236" t="n">
-        <v>-84.76971435546875</v>
+        <v>-84.71974182128906</v>
       </c>
     </row>
     <row r="237">
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D237" t="n">
-        <v>-131.4528961181641</v>
+        <v>-131.4025421142578</v>
       </c>
     </row>
     <row r="238">
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D238" t="n">
-        <v>-159.7869110107422</v>
+        <v>-159.7365570068359</v>
       </c>
     </row>
     <row r="239">
@@ -4252,10 +4252,10 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D239" t="n">
-        <v>-302.4006958007812</v>
+        <v>-302.350341796875</v>
       </c>
     </row>
     <row r="240">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D240" t="n">
-        <v>-318.4396667480469</v>
+        <v>-318.3893127441406</v>
       </c>
     </row>
     <row r="241">
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D241" t="n">
-        <v>-271.9054565429688</v>
+        <v>-271.8551025390625</v>
       </c>
     </row>
     <row r="242">
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D242" t="n">
-        <v>-175.7023773193359</v>
+        <v>-175.6520233154297</v>
       </c>
     </row>
     <row r="243">
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D243" t="n">
-        <v>-146.3844299316406</v>
+        <v>-146.3340759277344</v>
       </c>
     </row>
     <row r="244">
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D244" t="n">
-        <v>-75.5706787109375</v>
+        <v>-75.52070617675781</v>
       </c>
     </row>
     <row r="245">
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D245" t="n">
-        <v>-304.7924194335938</v>
+        <v>-304.7420654296875</v>
       </c>
     </row>
     <row r="246">
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D246" t="n">
-        <v>-138.6028289794922</v>
+        <v>-138.5524749755859</v>
       </c>
     </row>
     <row r="247">
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D247" t="n">
-        <v>-143.3622894287109</v>
+        <v>-143.3119354248047</v>
       </c>
     </row>
     <row r="248">
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D248" t="n">
-        <v>-170.1062316894531</v>
+        <v>-170.0558776855469</v>
       </c>
     </row>
     <row r="249">
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D249" t="n">
-        <v>-291.0875244140625</v>
+        <v>-291.0371704101562</v>
       </c>
     </row>
     <row r="250">
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D250" t="n">
-        <v>-138.205078125</v>
+        <v>-138.1547241210938</v>
       </c>
     </row>
     <row r="251">
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D251" t="n">
-        <v>-304.9995727539062</v>
+        <v>-304.94921875</v>
       </c>
     </row>
     <row r="252">
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D252" t="n">
-        <v>-73.49198913574219</v>
+        <v>-73.4420166015625</v>
       </c>
     </row>
     <row r="253">
@@ -4476,10 +4476,10 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D253" t="n">
-        <v>-281.7724304199219</v>
+        <v>-281.7220764160156</v>
       </c>
     </row>
     <row r="254">
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D254" t="n">
-        <v>-266.6674194335938</v>
+        <v>-266.6170654296875</v>
       </c>
     </row>
     <row r="255">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D255" t="n">
-        <v>-147.5298461914062</v>
+        <v>-147.4794921875</v>
       </c>
     </row>
     <row r="256">
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D256" t="n">
-        <v>-86.489013671875</v>
+        <v>-86.43904113769531</v>
       </c>
     </row>
     <row r="257">
@@ -4540,10 +4540,10 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D257" t="n">
-        <v>-87.83348083496094</v>
+        <v>-87.78350830078125</v>
       </c>
     </row>
     <row r="258">
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D258" t="n">
-        <v>-90.6356201171875</v>
+        <v>-90.58564758300781</v>
       </c>
     </row>
     <row r="259">
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D259" t="n">
-        <v>-80.94471740722656</v>
+        <v>-80.89474487304688</v>
       </c>
     </row>
     <row r="260">
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D260" t="n">
-        <v>-282.1936645507812</v>
+        <v>-282.143310546875</v>
       </c>
     </row>
     <row r="261">
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D261" t="n">
-        <v>-151.3356170654297</v>
+        <v>-151.2852630615234</v>
       </c>
     </row>
     <row r="262">
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D262" t="n">
-        <v>-135.5974731445312</v>
+        <v>-135.547119140625</v>
       </c>
     </row>
     <row r="263">
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D263" t="n">
-        <v>-156.1833343505859</v>
+        <v>-156.1329803466797</v>
       </c>
     </row>
     <row r="264">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D264" t="n">
-        <v>-143.1311187744141</v>
+        <v>-143.0807647705078</v>
       </c>
     </row>
     <row r="265">
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D265" t="n">
-        <v>-145.8213806152344</v>
+        <v>-145.7710266113281</v>
       </c>
     </row>
     <row r="266">
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>1</v>
+        <v>0.9503057599067688</v>
       </c>
       <c r="D266" t="n">
-        <v>-82.27571868896484</v>
+        <v>-82.22574615478516</v>
       </c>
     </row>
     <row r="267">
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D267" t="n">
-        <v>-232.36474609375</v>
+        <v>-232.3143920898438</v>
       </c>
     </row>
     <row r="268">
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D268" t="n">
-        <v>-141.3659515380859</v>
+        <v>-141.3155975341797</v>
       </c>
     </row>
     <row r="269">
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D269" t="n">
-        <v>-283.5233154296875</v>
+        <v>-283.4729614257812</v>
       </c>
     </row>
     <row r="270">
@@ -4748,10 +4748,10 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D270" t="n">
-        <v>-160.0604705810547</v>
+        <v>-160.0101165771484</v>
       </c>
     </row>
     <row r="271">
@@ -4764,10 +4764,10 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D271" t="n">
-        <v>-160.4057159423828</v>
+        <v>-160.3553619384766</v>
       </c>
     </row>
     <row r="272">
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D272" t="n">
-        <v>-144.7125091552734</v>
+        <v>-144.6621551513672</v>
       </c>
     </row>
     <row r="273">
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D273" t="n">
-        <v>-299.4589233398438</v>
+        <v>-299.4085693359375</v>
       </c>
     </row>
     <row r="274">
@@ -4812,10 +4812,10 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D274" t="n">
-        <v>-305.8491821289062</v>
+        <v>-305.798828125</v>
       </c>
     </row>
     <row r="275">
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D275" t="n">
-        <v>-297.4778137207031</v>
+        <v>-297.4274597167969</v>
       </c>
     </row>
     <row r="276">
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D276" t="n">
-        <v>-150.7125854492188</v>
+        <v>-150.6622314453125</v>
       </c>
     </row>
     <row r="277">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D277" t="n">
-        <v>-152.8955688476562</v>
+        <v>-152.84521484375</v>
       </c>
     </row>
     <row r="278">
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D278" t="n">
-        <v>-295.0179138183594</v>
+        <v>-294.9675598144531</v>
       </c>
     </row>
     <row r="279">
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D279" t="n">
-        <v>-134.8380126953125</v>
+        <v>-134.7876586914062</v>
       </c>
     </row>
     <row r="280">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D280" t="n">
-        <v>-159.0217132568359</v>
+        <v>-158.9713592529297</v>
       </c>
     </row>
     <row r="281">
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D281" t="n">
-        <v>-137.7362670898438</v>
+        <v>-137.6859130859375</v>
       </c>
     </row>
     <row r="282">
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D282" t="n">
-        <v>-169.0542297363281</v>
+        <v>-169.0038757324219</v>
       </c>
     </row>
     <row r="283">
@@ -4956,10 +4956,10 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D283" t="n">
-        <v>-285.314453125</v>
+        <v>-285.2640991210938</v>
       </c>
     </row>
     <row r="284">
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D284" t="n">
-        <v>-164.6370849609375</v>
+        <v>-164.5867309570312</v>
       </c>
     </row>
     <row r="285">
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D285" t="n">
-        <v>-155.3954467773438</v>
+        <v>-155.3450927734375</v>
       </c>
     </row>
     <row r="286">
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D286" t="n">
-        <v>-156.4569091796875</v>
+        <v>-156.4065551757812</v>
       </c>
     </row>
     <row r="287">
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>4</v>
+        <v>3.950075387954712</v>
       </c>
       <c r="D287" t="n">
-        <v>-260.8756103515625</v>
+        <v>-260.8252563476562</v>
       </c>
     </row>
     <row r="288">
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D288" t="n">
-        <v>-144.0422821044922</v>
+        <v>-143.9919281005859</v>
       </c>
     </row>
     <row r="289">
@@ -5052,10 +5052,10 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D289" t="n">
-        <v>-150.1921081542969</v>
+        <v>-150.1417541503906</v>
       </c>
     </row>
     <row r="290">
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D290" t="n">
-        <v>-147.0261688232422</v>
+        <v>-146.9758148193359</v>
       </c>
     </row>
     <row r="291">
@@ -5084,10 +5084,10 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>2</v>
+        <v>1.950151324272156</v>
       </c>
       <c r="D291" t="n">
-        <v>-138.6236114501953</v>
+        <v>-138.5732574462891</v>
       </c>
     </row>
   </sheetData>

--- a/dps_params.xlsx
+++ b/dps_params.xlsx
@@ -463,7 +463,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D2" t="n">
-        <v>-312.7254333496094</v>
+        <v>-309.1005859375</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D3" t="n">
-        <v>-131.4637298583984</v>
+        <v>-134.9738159179688</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D4" t="n">
-        <v>-75.83651733398438</v>
+        <v>-82.71351623535156</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D5" t="n">
-        <v>-94.05818176269531</v>
+        <v>-93.22376251220703</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D6" t="n">
-        <v>-280.8211059570312</v>
+        <v>-280.7464904785156</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D7" t="n">
-        <v>-85.18466949462891</v>
+        <v>-82.42974090576172</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D8" t="n">
-        <v>-67.7978515625</v>
+        <v>-67.80724334716797</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D9" t="n">
-        <v>-77.66989135742188</v>
+        <v>-76.08240509033203</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D10" t="n">
-        <v>-70.27727508544922</v>
+        <v>-64.091552734375</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D11" t="n">
-        <v>-75.27584075927734</v>
+        <v>-80.95470428466797</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D12" t="n">
-        <v>-236.6438751220703</v>
+        <v>-243.3041076660156</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D13" t="n">
-        <v>-78.96727752685547</v>
+        <v>-82.53105926513672</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D14" t="n">
-        <v>-162.1129913330078</v>
+        <v>-160.8441925048828</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D15" t="n">
-        <v>-82.48619079589844</v>
+        <v>-80.24419403076172</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D16" t="n">
-        <v>-76.80584716796875</v>
+        <v>-79.67259979248047</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D17" t="n">
-        <v>-141.8783111572266</v>
+        <v>-142.6751251220703</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D18" t="n">
-        <v>-172.1153564453125</v>
+        <v>-166.5413818359375</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D19" t="n">
-        <v>-85.71772766113281</v>
+        <v>-89.59226989746094</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D20" t="n">
-        <v>-133.6965179443359</v>
+        <v>-130.2058410644531</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D21" t="n">
-        <v>-75.57963562011719</v>
+        <v>-78.82199859619141</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D22" t="n">
-        <v>-153.8601684570312</v>
+        <v>-154.7782287597656</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D23" t="n">
-        <v>-80.62969207763672</v>
+        <v>-71.24940490722656</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D24" t="n">
-        <v>-84.37356567382812</v>
+        <v>-80.9686279296875</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D25" t="n">
-        <v>-82.66513824462891</v>
+        <v>-75.10494995117188</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D26" t="n">
-        <v>-80.98927307128906</v>
+        <v>-75.36362457275391</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D27" t="n">
-        <v>-304.7078247070312</v>
+        <v>-300.4784851074219</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D28" t="n">
-        <v>-160.7868804931641</v>
+        <v>-160.10986328125</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D29" t="n">
-        <v>-283.2989501953125</v>
+        <v>-281.6161499023438</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D30" t="n">
-        <v>-293.0727233886719</v>
+        <v>-287.6835327148438</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D31" t="n">
-        <v>-87.63692474365234</v>
+        <v>-88.76457977294922</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D32" t="n">
-        <v>-66.37998962402344</v>
+        <v>-66.57224273681641</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +959,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D33" t="n">
-        <v>-238.753662109375</v>
+        <v>-237.9556579589844</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +975,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D34" t="n">
-        <v>-273.0565490722656</v>
+        <v>-266.1702270507812</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D35" t="n">
-        <v>-86.87876892089844</v>
+        <v>-85.30931091308594</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D36" t="n">
-        <v>-79.56106567382812</v>
+        <v>-81.43650054931641</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D37" t="n">
-        <v>-147.7458953857422</v>
+        <v>-140.2850952148438</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1039,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D38" t="n">
-        <v>-139.0149230957031</v>
+        <v>-140.8331756591797</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D39" t="n">
-        <v>-80.09745788574219</v>
+        <v>-82.94212341308594</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D40" t="n">
-        <v>-143.8488159179688</v>
+        <v>-147.6476440429688</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D41" t="n">
-        <v>-137.1827239990234</v>
+        <v>-137.0538330078125</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1103,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D42" t="n">
-        <v>-89.4154052734375</v>
+        <v>-86.39736175537109</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1119,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D43" t="n">
-        <v>-78.84846496582031</v>
+        <v>-78.404296875</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D44" t="n">
-        <v>-149.2010345458984</v>
+        <v>-153.6472473144531</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1151,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D45" t="n">
-        <v>-79.47753143310547</v>
+        <v>-74.35928344726562</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1167,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D46" t="n">
-        <v>-301.5950317382812</v>
+        <v>-310.0749816894531</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1183,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D47" t="n">
-        <v>-80.33058929443359</v>
+        <v>-76.91171264648438</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D48" t="n">
-        <v>-251.1686248779297</v>
+        <v>-254.4338226318359</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1215,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D49" t="n">
-        <v>-222.0537567138672</v>
+        <v>-230.6791839599609</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1231,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D50" t="n">
-        <v>-140.1004028320312</v>
+        <v>-141.214111328125</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1247,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D51" t="n">
-        <v>-79.77919769287109</v>
+        <v>-79.84412384033203</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1263,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D52" t="n">
-        <v>-146.82177734375</v>
+        <v>-148.6996765136719</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1279,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D53" t="n">
-        <v>-82.98794555664062</v>
+        <v>-78.21106719970703</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1295,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D54" t="n">
-        <v>-88.12543487548828</v>
+        <v>-83.91950988769531</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D55" t="n">
-        <v>-170.7263641357422</v>
+        <v>-164.7897033691406</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1327,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D56" t="n">
-        <v>-140.1126403808594</v>
+        <v>-136.6848907470703</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1343,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D57" t="n">
-        <v>-79.75038909912109</v>
+        <v>-74.77757263183594</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1359,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D58" t="n">
-        <v>-242.3766479492188</v>
+        <v>-233.1331939697266</v>
       </c>
     </row>
     <row r="59">
@@ -1375,7 +1375,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D59" t="n">
-        <v>-127.6420135498047</v>
+        <v>-128.4257659912109</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1391,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D60" t="n">
-        <v>-258.9076538085938</v>
+        <v>-254.5596008300781</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1407,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D61" t="n">
-        <v>-172.2388610839844</v>
+        <v>-164.9859924316406</v>
       </c>
     </row>
     <row r="62">
@@ -1423,7 +1423,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D62" t="n">
-        <v>-85.45381164550781</v>
+        <v>-83.81652069091797</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1439,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D63" t="n">
-        <v>-118.5802230834961</v>
+        <v>-120.5479965209961</v>
       </c>
     </row>
     <row r="64">
@@ -1455,7 +1455,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D64" t="n">
-        <v>-83.94557952880859</v>
+        <v>-82.81270599365234</v>
       </c>
     </row>
     <row r="65">
@@ -1471,7 +1471,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D65" t="n">
-        <v>-168.9167633056641</v>
+        <v>-171.1607513427734</v>
       </c>
     </row>
     <row r="66">
@@ -1487,7 +1487,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D66" t="n">
-        <v>-128.8504943847656</v>
+        <v>-132.3807373046875</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1503,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D67" t="n">
-        <v>-140.9205780029297</v>
+        <v>-133.0077362060547</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1519,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D68" t="n">
-        <v>-78.54950714111328</v>
+        <v>-82.77093505859375</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1535,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D69" t="n">
-        <v>-139.7522125244141</v>
+        <v>-136.5610656738281</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1551,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D70" t="n">
-        <v>-76.36381530761719</v>
+        <v>-78.45337677001953</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1567,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D71" t="n">
-        <v>-81.62059783935547</v>
+        <v>-80.37123870849609</v>
       </c>
     </row>
     <row r="72">
@@ -1583,7 +1583,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D72" t="n">
-        <v>-328.6170959472656</v>
+        <v>-328.58056640625</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1599,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D73" t="n">
-        <v>-134.1955108642578</v>
+        <v>-136.0906524658203</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1615,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D74" t="n">
-        <v>-74.15227508544922</v>
+        <v>-74.64193725585938</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1631,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D75" t="n">
-        <v>-118.1296615600586</v>
+        <v>-120.3774337768555</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1647,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D76" t="n">
-        <v>-123.8286056518555</v>
+        <v>-126.8474960327148</v>
       </c>
     </row>
     <row r="77">
@@ -1663,7 +1663,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D77" t="n">
-        <v>-247.5119171142578</v>
+        <v>-252.5020751953125</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1679,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D78" t="n">
-        <v>-154.3571014404297</v>
+        <v>-159.7727966308594</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1695,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D79" t="n">
-        <v>-146.1668853759766</v>
+        <v>-150.5826873779297</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1711,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D80" t="n">
-        <v>-159.6837768554688</v>
+        <v>-155.6047515869141</v>
       </c>
     </row>
     <row r="81">
@@ -1727,7 +1727,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D81" t="n">
-        <v>-216.9677886962891</v>
+        <v>-207.5214691162109</v>
       </c>
     </row>
     <row r="82">
@@ -1743,7 +1743,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D82" t="n">
-        <v>-153.8559112548828</v>
+        <v>-155.3805999755859</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1759,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D83" t="n">
-        <v>-321.413818359375</v>
+        <v>-318.6242370605469</v>
       </c>
     </row>
     <row r="84">
@@ -1775,7 +1775,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D84" t="n">
-        <v>-89.27260589599609</v>
+        <v>-89.33515930175781</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1791,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D85" t="n">
-        <v>-141.107666015625</v>
+        <v>-137.5792236328125</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1807,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D86" t="n">
-        <v>-76.42369079589844</v>
+        <v>-74.06844329833984</v>
       </c>
     </row>
     <row r="87">
@@ -1823,7 +1823,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D87" t="n">
-        <v>-126.181282043457</v>
+        <v>-130.358154296875</v>
       </c>
     </row>
     <row r="88">
@@ -1839,7 +1839,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D88" t="n">
-        <v>-146.5907897949219</v>
+        <v>-148.867431640625</v>
       </c>
     </row>
     <row r="89">
@@ -1855,7 +1855,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D89" t="n">
-        <v>-281.5341491699219</v>
+        <v>-280.9424438476562</v>
       </c>
     </row>
     <row r="90">
@@ -1871,7 +1871,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D90" t="n">
-        <v>-158.0813751220703</v>
+        <v>-149.569091796875</v>
       </c>
     </row>
     <row r="91">
@@ -1887,7 +1887,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D91" t="n">
-        <v>-83.41325378417969</v>
+        <v>-78.58026885986328</v>
       </c>
     </row>
     <row r="92">
@@ -1903,7 +1903,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D92" t="n">
-        <v>-142.9463806152344</v>
+        <v>-145.5185852050781</v>
       </c>
     </row>
     <row r="93">
@@ -1919,7 +1919,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D93" t="n">
-        <v>-136.2249145507812</v>
+        <v>-138.2600708007812</v>
       </c>
     </row>
     <row r="94">
@@ -1935,7 +1935,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D94" t="n">
-        <v>-287.7788391113281</v>
+        <v>-285.8060607910156</v>
       </c>
     </row>
     <row r="95">
@@ -1951,7 +1951,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D95" t="n">
-        <v>-133.0156097412109</v>
+        <v>-137.5745239257812</v>
       </c>
     </row>
     <row r="96">
@@ -1967,7 +1967,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D96" t="n">
-        <v>-137.7474670410156</v>
+        <v>-132.6447296142578</v>
       </c>
     </row>
     <row r="97">
@@ -1983,7 +1983,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D97" t="n">
-        <v>-77.11904144287109</v>
+        <v>-75.90840148925781</v>
       </c>
     </row>
     <row r="98">
@@ -1999,7 +1999,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D98" t="n">
-        <v>-141.9716186523438</v>
+        <v>-138.3424377441406</v>
       </c>
     </row>
     <row r="99">
@@ -2015,7 +2015,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D99" t="n">
-        <v>-152.9307708740234</v>
+        <v>-162.0659027099609</v>
       </c>
     </row>
     <row r="100">
@@ -2031,7 +2031,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D100" t="n">
-        <v>-165.0157318115234</v>
+        <v>-165.9186706542969</v>
       </c>
     </row>
     <row r="101">
@@ -2047,7 +2047,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D101" t="n">
-        <v>-268.0355224609375</v>
+        <v>-257.6102600097656</v>
       </c>
     </row>
     <row r="102">
@@ -2063,7 +2063,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D102" t="n">
-        <v>-84.37002563476562</v>
+        <v>-78.45462036132812</v>
       </c>
     </row>
     <row r="103">
@@ -2079,7 +2079,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D103" t="n">
-        <v>-114.6757354736328</v>
+        <v>-123.7591552734375</v>
       </c>
     </row>
     <row r="104">
@@ -2095,7 +2095,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D104" t="n">
-        <v>-83.70468902587891</v>
+        <v>-76.48342132568359</v>
       </c>
     </row>
     <row r="105">
@@ -2111,7 +2111,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D105" t="n">
-        <v>-156.8477630615234</v>
+        <v>-160.1502990722656</v>
       </c>
     </row>
     <row r="106">
@@ -2127,7 +2127,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D106" t="n">
-        <v>-120.8411483764648</v>
+        <v>-120.1368637084961</v>
       </c>
     </row>
     <row r="107">
@@ -2143,7 +2143,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D107" t="n">
-        <v>-155.2736358642578</v>
+        <v>-153.9892730712891</v>
       </c>
     </row>
     <row r="108">
@@ -2159,7 +2159,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D108" t="n">
-        <v>-303.7373962402344</v>
+        <v>-309.4504089355469</v>
       </c>
     </row>
     <row r="109">
@@ -2175,7 +2175,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D109" t="n">
-        <v>-125.6840667724609</v>
+        <v>-118.4346160888672</v>
       </c>
     </row>
     <row r="110">
@@ -2191,7 +2191,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D110" t="n">
-        <v>-89.44441223144531</v>
+        <v>-92.11170959472656</v>
       </c>
     </row>
     <row r="111">
@@ -2207,7 +2207,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D111" t="n">
-        <v>-80.51302337646484</v>
+        <v>-75.29190826416016</v>
       </c>
     </row>
     <row r="112">
@@ -2223,7 +2223,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D112" t="n">
-        <v>-124.8562622070312</v>
+        <v>-122.1351318359375</v>
       </c>
     </row>
     <row r="113">
@@ -2239,7 +2239,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D113" t="n">
-        <v>-166.8563385009766</v>
+        <v>-169.1813049316406</v>
       </c>
     </row>
     <row r="114">
@@ -2255,7 +2255,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D114" t="n">
-        <v>-84.69362640380859</v>
+        <v>-89.54834747314453</v>
       </c>
     </row>
     <row r="115">
@@ -2271,7 +2271,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D115" t="n">
-        <v>-313.0234069824219</v>
+        <v>-320.4349365234375</v>
       </c>
     </row>
     <row r="116">
@@ -2287,7 +2287,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D116" t="n">
-        <v>-83.94857788085938</v>
+        <v>-86.90085601806641</v>
       </c>
     </row>
     <row r="117">
@@ -2303,7 +2303,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D117" t="n">
-        <v>-328.5974426269531</v>
+        <v>-340.40087890625</v>
       </c>
     </row>
     <row r="118">
@@ -2319,7 +2319,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D118" t="n">
-        <v>-76.90480041503906</v>
+        <v>-77.21125793457031</v>
       </c>
     </row>
     <row r="119">
@@ -2335,7 +2335,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D119" t="n">
-        <v>-295.2546997070312</v>
+        <v>-299.3388366699219</v>
       </c>
     </row>
     <row r="120">
@@ -2351,7 +2351,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D120" t="n">
-        <v>-153.3353729248047</v>
+        <v>-143.9611968994141</v>
       </c>
     </row>
     <row r="121">
@@ -2367,7 +2367,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D121" t="n">
-        <v>-82.33835601806641</v>
+        <v>-75.96382141113281</v>
       </c>
     </row>
     <row r="122">
@@ -2383,7 +2383,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D122" t="n">
-        <v>-164.1570892333984</v>
+        <v>-166.0923156738281</v>
       </c>
     </row>
     <row r="123">
@@ -2399,7 +2399,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D123" t="n">
-        <v>-76.22636413574219</v>
+        <v>-72.10225677490234</v>
       </c>
     </row>
     <row r="124">
@@ -2415,7 +2415,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D124" t="n">
-        <v>-76.74578094482422</v>
+        <v>-79.17037200927734</v>
       </c>
     </row>
     <row r="125">
@@ -2431,7 +2431,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D125" t="n">
-        <v>-149.8813018798828</v>
+        <v>-148.9383392333984</v>
       </c>
     </row>
     <row r="126">
@@ -2447,7 +2447,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D126" t="n">
-        <v>-160.6069183349609</v>
+        <v>-157.4638824462891</v>
       </c>
     </row>
     <row r="127">
@@ -2463,7 +2463,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D127" t="n">
-        <v>-111.405517578125</v>
+        <v>-108.0466461181641</v>
       </c>
     </row>
     <row r="128">
@@ -2479,7 +2479,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D128" t="n">
-        <v>-159.3714752197266</v>
+        <v>-155.8766784667969</v>
       </c>
     </row>
     <row r="129">
@@ -2495,7 +2495,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D129" t="n">
-        <v>-320.8700561523438</v>
+        <v>-320.9447631835938</v>
       </c>
     </row>
     <row r="130">
@@ -2511,7 +2511,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D130" t="n">
-        <v>-74.71963500976562</v>
+        <v>-74.12855529785156</v>
       </c>
     </row>
     <row r="131">
@@ -2527,7 +2527,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D131" t="n">
-        <v>-79.41609954833984</v>
+        <v>-84.84364318847656</v>
       </c>
     </row>
     <row r="132">
@@ -2543,7 +2543,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D132" t="n">
-        <v>-77.03787994384766</v>
+        <v>-72.13954162597656</v>
       </c>
     </row>
     <row r="133">
@@ -2559,7 +2559,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D133" t="n">
-        <v>-82.21346282958984</v>
+        <v>-86.53540802001953</v>
       </c>
     </row>
     <row r="134">
@@ -2575,7 +2575,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D134" t="n">
-        <v>-65.51644134521484</v>
+        <v>-66.52980041503906</v>
       </c>
     </row>
     <row r="135">
@@ -2591,7 +2591,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D135" t="n">
-        <v>-287.1722717285156</v>
+        <v>-293.3295593261719</v>
       </c>
     </row>
     <row r="136">
@@ -2607,7 +2607,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D136" t="n">
-        <v>-279.1708679199219</v>
+        <v>-283.2849426269531</v>
       </c>
     </row>
     <row r="137">
@@ -2623,7 +2623,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D137" t="n">
-        <v>-146.5892028808594</v>
+        <v>-148.4869995117188</v>
       </c>
     </row>
     <row r="138">
@@ -2639,7 +2639,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D138" t="n">
-        <v>-76.09178924560547</v>
+        <v>-72.57636260986328</v>
       </c>
     </row>
     <row r="139">
@@ -2655,7 +2655,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D139" t="n">
-        <v>-283.7149353027344</v>
+        <v>-295.8775024414062</v>
       </c>
     </row>
     <row r="140">
@@ -2671,7 +2671,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D140" t="n">
-        <v>-112.5919647216797</v>
+        <v>-116.2997131347656</v>
       </c>
     </row>
     <row r="141">
@@ -2687,7 +2687,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D141" t="n">
-        <v>-88.67609405517578</v>
+        <v>-87.99012756347656</v>
       </c>
     </row>
     <row r="142">
@@ -2703,7 +2703,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D142" t="n">
-        <v>-154.3295593261719</v>
+        <v>-152.5202941894531</v>
       </c>
     </row>
     <row r="143">
@@ -2719,7 +2719,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D143" t="n">
-        <v>-141.0936584472656</v>
+        <v>-144.5496978759766</v>
       </c>
     </row>
     <row r="144">
@@ -2735,7 +2735,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D144" t="n">
-        <v>-271.0507507324219</v>
+        <v>-281.1041259765625</v>
       </c>
     </row>
     <row r="145">
@@ -2751,7 +2751,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D145" t="n">
-        <v>-122.0592422485352</v>
+        <v>-128.2061157226562</v>
       </c>
     </row>
     <row r="146">
@@ -2767,7 +2767,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D146" t="n">
-        <v>-76.87986755371094</v>
+        <v>-78.88609313964844</v>
       </c>
     </row>
     <row r="147">
@@ -2783,7 +2783,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D147" t="n">
-        <v>-166.8616180419922</v>
+        <v>-172.4825134277344</v>
       </c>
     </row>
     <row r="148">
@@ -2799,7 +2799,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D148" t="n">
-        <v>-77.47758483886719</v>
+        <v>-77.35348510742188</v>
       </c>
     </row>
     <row r="149">
@@ -2815,7 +2815,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D149" t="n">
-        <v>-262.2435913085938</v>
+        <v>-262.7428894042969</v>
       </c>
     </row>
     <row r="150">
@@ -2831,7 +2831,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D150" t="n">
-        <v>-157.5698547363281</v>
+        <v>-148.1756439208984</v>
       </c>
     </row>
     <row r="151">
@@ -2847,7 +2847,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D151" t="n">
-        <v>-129.7572174072266</v>
+        <v>-131.1627960205078</v>
       </c>
     </row>
     <row r="152">
@@ -2863,7 +2863,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D152" t="n">
-        <v>-83.46860504150391</v>
+        <v>-84.46334838867188</v>
       </c>
     </row>
     <row r="153">
@@ -2879,7 +2879,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D153" t="n">
-        <v>-136.1714782714844</v>
+        <v>-141.6422119140625</v>
       </c>
     </row>
     <row r="154">
@@ -2895,7 +2895,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D154" t="n">
-        <v>-81.06667327880859</v>
+        <v>-79.89212799072266</v>
       </c>
     </row>
     <row r="155">
@@ -2911,7 +2911,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D155" t="n">
-        <v>-124.8697052001953</v>
+        <v>-121.1758728027344</v>
       </c>
     </row>
     <row r="156">
@@ -2927,7 +2927,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D156" t="n">
-        <v>-150.8552703857422</v>
+        <v>-151.0342407226562</v>
       </c>
     </row>
     <row r="157">
@@ -2943,7 +2943,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D157" t="n">
-        <v>-166.4446716308594</v>
+        <v>-164.8954620361328</v>
       </c>
     </row>
     <row r="158">
@@ -2959,7 +2959,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D158" t="n">
-        <v>-221.4796142578125</v>
+        <v>-214.7956695556641</v>
       </c>
     </row>
     <row r="159">
@@ -2975,7 +2975,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D159" t="n">
-        <v>-161.7942657470703</v>
+        <v>-165.8010101318359</v>
       </c>
     </row>
     <row r="160">
@@ -2991,7 +2991,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D160" t="n">
-        <v>-77.43194580078125</v>
+        <v>-82.24082183837891</v>
       </c>
     </row>
     <row r="161">
@@ -3007,7 +3007,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D161" t="n">
-        <v>-165.3012084960938</v>
+        <v>-167.3715515136719</v>
       </c>
     </row>
     <row r="162">
@@ -3023,7 +3023,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D162" t="n">
-        <v>-167.9928436279297</v>
+        <v>-171.0347137451172</v>
       </c>
     </row>
     <row r="163">
@@ -3039,7 +3039,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D163" t="n">
-        <v>-78.91123962402344</v>
+        <v>-84.91159820556641</v>
       </c>
     </row>
     <row r="164">
@@ -3055,7 +3055,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D164" t="n">
-        <v>-140.7919769287109</v>
+        <v>-136.9749755859375</v>
       </c>
     </row>
     <row r="165">
@@ -3071,7 +3071,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D165" t="n">
-        <v>-142.3471221923828</v>
+        <v>-139.6933746337891</v>
       </c>
     </row>
     <row r="166">
@@ -3087,7 +3087,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D166" t="n">
-        <v>-123.1463623046875</v>
+        <v>-118.5795822143555</v>
       </c>
     </row>
     <row r="167">
@@ -3103,7 +3103,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D167" t="n">
-        <v>-68.00828552246094</v>
+        <v>-67.81723022460938</v>
       </c>
     </row>
     <row r="168">
@@ -3119,7 +3119,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D168" t="n">
-        <v>-150.3597717285156</v>
+        <v>-155.0774078369141</v>
       </c>
     </row>
     <row r="169">
@@ -3135,7 +3135,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D169" t="n">
-        <v>-72.07534027099609</v>
+        <v>-74.20499420166016</v>
       </c>
     </row>
     <row r="170">
@@ -3151,7 +3151,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D170" t="n">
-        <v>-81.48613739013672</v>
+        <v>-83.50370025634766</v>
       </c>
     </row>
     <row r="171">
@@ -3167,7 +3167,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D171" t="n">
-        <v>-94.90351867675781</v>
+        <v>-94.27629089355469</v>
       </c>
     </row>
     <row r="172">
@@ -3183,7 +3183,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D172" t="n">
-        <v>-81.62312316894531</v>
+        <v>-77.2379150390625</v>
       </c>
     </row>
     <row r="173">
@@ -3199,7 +3199,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D173" t="n">
-        <v>-310.9585571289062</v>
+        <v>-301.1980895996094</v>
       </c>
     </row>
     <row r="174">
@@ -3215,7 +3215,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D174" t="n">
-        <v>-83.18436431884766</v>
+        <v>-82.49371337890625</v>
       </c>
     </row>
     <row r="175">
@@ -3231,7 +3231,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D175" t="n">
-        <v>-159.8742065429688</v>
+        <v>-160.7684783935547</v>
       </c>
     </row>
     <row r="176">
@@ -3247,7 +3247,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D176" t="n">
-        <v>-291.7589721679688</v>
+        <v>-291.9177856445312</v>
       </c>
     </row>
     <row r="177">
@@ -3263,7 +3263,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D177" t="n">
-        <v>-132.8778839111328</v>
+        <v>-139.9996337890625</v>
       </c>
     </row>
     <row r="178">
@@ -3279,7 +3279,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D178" t="n">
-        <v>-156.6101989746094</v>
+        <v>-150.8725891113281</v>
       </c>
     </row>
     <row r="179">
@@ -3295,7 +3295,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D179" t="n">
-        <v>-304.3458251953125</v>
+        <v>-296.6404418945312</v>
       </c>
     </row>
     <row r="180">
@@ -3311,7 +3311,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D180" t="n">
-        <v>-156.8587341308594</v>
+        <v>-157.0292816162109</v>
       </c>
     </row>
     <row r="181">
@@ -3327,7 +3327,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D181" t="n">
-        <v>-83.33131408691406</v>
+        <v>-90.44426727294922</v>
       </c>
     </row>
     <row r="182">
@@ -3343,7 +3343,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D182" t="n">
-        <v>-130.4503936767578</v>
+        <v>-131.5960998535156</v>
       </c>
     </row>
     <row r="183">
@@ -3359,7 +3359,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D183" t="n">
-        <v>-79.63169860839844</v>
+        <v>-74.22304534912109</v>
       </c>
     </row>
     <row r="184">
@@ -3375,7 +3375,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D184" t="n">
-        <v>-223.1320037841797</v>
+        <v>-208.8701629638672</v>
       </c>
     </row>
     <row r="185">
@@ -3391,7 +3391,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D185" t="n">
-        <v>-164.3846130371094</v>
+        <v>-166.1147766113281</v>
       </c>
     </row>
     <row r="186">
@@ -3407,7 +3407,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D186" t="n">
-        <v>-147.887451171875</v>
+        <v>-140.179931640625</v>
       </c>
     </row>
     <row r="187">
@@ -3423,7 +3423,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D187" t="n">
-        <v>-159.8807373046875</v>
+        <v>-161.0829162597656</v>
       </c>
     </row>
     <row r="188">
@@ -3439,7 +3439,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D188" t="n">
-        <v>-144.4764709472656</v>
+        <v>-144.1911163330078</v>
       </c>
     </row>
     <row r="189">
@@ -3455,7 +3455,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D189" t="n">
-        <v>-72.46682739257812</v>
+        <v>-77.34550476074219</v>
       </c>
     </row>
     <row r="190">
@@ -3471,7 +3471,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D190" t="n">
-        <v>-263.897705078125</v>
+        <v>-262.3949890136719</v>
       </c>
     </row>
     <row r="191">
@@ -3487,7 +3487,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D191" t="n">
-        <v>-124.8207397460938</v>
+        <v>-118.271369934082</v>
       </c>
     </row>
     <row r="192">
@@ -3503,7 +3503,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D192" t="n">
-        <v>-76.70564270019531</v>
+        <v>-76.62386322021484</v>
       </c>
     </row>
     <row r="193">
@@ -3519,7 +3519,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D193" t="n">
-        <v>-81.99093627929688</v>
+        <v>-89.00557708740234</v>
       </c>
     </row>
     <row r="194">
@@ -3535,7 +3535,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D194" t="n">
-        <v>-155.4027709960938</v>
+        <v>-157.7405242919922</v>
       </c>
     </row>
     <row r="195">
@@ -3551,7 +3551,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D195" t="n">
-        <v>-303.3152465820312</v>
+        <v>-302.0237426757812</v>
       </c>
     </row>
     <row r="196">
@@ -3567,7 +3567,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D196" t="n">
-        <v>-319.9754943847656</v>
+        <v>-327.6971435546875</v>
       </c>
     </row>
     <row r="197">
@@ -3583,7 +3583,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D197" t="n">
-        <v>-77.75380706787109</v>
+        <v>-74.89505004882812</v>
       </c>
     </row>
     <row r="198">
@@ -3599,7 +3599,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D198" t="n">
-        <v>-155.2261962890625</v>
+        <v>-154.8497619628906</v>
       </c>
     </row>
     <row r="199">
@@ -3615,7 +3615,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D199" t="n">
-        <v>-128.7209014892578</v>
+        <v>-129.0349884033203</v>
       </c>
     </row>
     <row r="200">
@@ -3631,7 +3631,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D200" t="n">
-        <v>-139.4406280517578</v>
+        <v>-146.6505737304688</v>
       </c>
     </row>
     <row r="201">
@@ -3647,7 +3647,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D201" t="n">
-        <v>-321.3683471679688</v>
+        <v>-322.7165832519531</v>
       </c>
     </row>
     <row r="202">
@@ -3663,7 +3663,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D202" t="n">
-        <v>-155.4756927490234</v>
+        <v>-156.9488372802734</v>
       </c>
     </row>
     <row r="203">
@@ -3679,7 +3679,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D203" t="n">
-        <v>-79.29045104980469</v>
+        <v>-77.00862121582031</v>
       </c>
     </row>
     <row r="204">
@@ -3695,7 +3695,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D204" t="n">
-        <v>-297.2643127441406</v>
+        <v>-301.7877807617188</v>
       </c>
     </row>
     <row r="205">
@@ -3711,7 +3711,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D205" t="n">
-        <v>-82.78701019287109</v>
+        <v>-84.99755096435547</v>
       </c>
     </row>
     <row r="206">
@@ -3727,7 +3727,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D206" t="n">
-        <v>-78.75799560546875</v>
+        <v>-80.08274078369141</v>
       </c>
     </row>
     <row r="207">
@@ -3743,7 +3743,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D207" t="n">
-        <v>-167.8619537353516</v>
+        <v>-163.7175598144531</v>
       </c>
     </row>
     <row r="208">
@@ -3759,7 +3759,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D208" t="n">
-        <v>-128.9341583251953</v>
+        <v>-127.7134552001953</v>
       </c>
     </row>
     <row r="209">
@@ -3775,7 +3775,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D209" t="n">
-        <v>-126.9077224731445</v>
+        <v>-126.5168685913086</v>
       </c>
     </row>
     <row r="210">
@@ -3791,7 +3791,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D210" t="n">
-        <v>-140.2141265869141</v>
+        <v>-144.1323699951172</v>
       </c>
     </row>
     <row r="211">
@@ -3807,7 +3807,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D211" t="n">
-        <v>-109.3126602172852</v>
+        <v>-105.1728210449219</v>
       </c>
     </row>
     <row r="212">
@@ -3823,7 +3823,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D212" t="n">
-        <v>-86.48761749267578</v>
+        <v>-92.96170043945312</v>
       </c>
     </row>
     <row r="213">
@@ -3839,7 +3839,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D213" t="n">
-        <v>-73.10427093505859</v>
+        <v>-80.58625030517578</v>
       </c>
     </row>
     <row r="214">
@@ -3855,7 +3855,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D214" t="n">
-        <v>-142.7543182373047</v>
+        <v>-149.4194488525391</v>
       </c>
     </row>
     <row r="215">
@@ -3871,7 +3871,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D215" t="n">
-        <v>-95.76849365234375</v>
+        <v>-95.29007720947266</v>
       </c>
     </row>
     <row r="216">
@@ -3887,7 +3887,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D216" t="n">
-        <v>-147.9821929931641</v>
+        <v>-142.8908386230469</v>
       </c>
     </row>
     <row r="217">
@@ -3903,7 +3903,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D217" t="n">
-        <v>-139.6598205566406</v>
+        <v>-144.3242034912109</v>
       </c>
     </row>
     <row r="218">
@@ -3919,7 +3919,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D218" t="n">
-        <v>-147.9880676269531</v>
+        <v>-147.9944763183594</v>
       </c>
     </row>
     <row r="219">
@@ -3935,7 +3935,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D219" t="n">
-        <v>-134.5063629150391</v>
+        <v>-139.4838714599609</v>
       </c>
     </row>
     <row r="220">
@@ -3951,7 +3951,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D220" t="n">
-        <v>-143.5470275878906</v>
+        <v>-142.4095001220703</v>
       </c>
     </row>
     <row r="221">
@@ -3967,7 +3967,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D221" t="n">
-        <v>-154.29638671875</v>
+        <v>-153.9279174804688</v>
       </c>
     </row>
     <row r="222">
@@ -3983,7 +3983,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D222" t="n">
-        <v>-143.8585052490234</v>
+        <v>-139.9765472412109</v>
       </c>
     </row>
     <row r="223">
@@ -3999,7 +3999,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D223" t="n">
-        <v>-93.94898986816406</v>
+        <v>-88.49543762207031</v>
       </c>
     </row>
     <row r="224">
@@ -4015,7 +4015,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D224" t="n">
-        <v>-78.51760864257812</v>
+        <v>-80.99088287353516</v>
       </c>
     </row>
     <row r="225">
@@ -4031,7 +4031,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D225" t="n">
-        <v>-76.15287780761719</v>
+        <v>-84.29518890380859</v>
       </c>
     </row>
     <row r="226">
@@ -4047,7 +4047,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D226" t="n">
-        <v>-144.0484161376953</v>
+        <v>-146.6853179931641</v>
       </c>
     </row>
     <row r="227">
@@ -4063,7 +4063,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D227" t="n">
-        <v>-86.96183776855469</v>
+        <v>-78.41032409667969</v>
       </c>
     </row>
     <row r="228">
@@ -4079,7 +4079,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D228" t="n">
-        <v>-147.1962890625</v>
+        <v>-147.2547760009766</v>
       </c>
     </row>
     <row r="229">
@@ -4095,7 +4095,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D229" t="n">
-        <v>-89.88682556152344</v>
+        <v>-95.97320556640625</v>
       </c>
     </row>
     <row r="230">
@@ -4111,7 +4111,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D230" t="n">
-        <v>-131.5116119384766</v>
+        <v>-137.4710540771484</v>
       </c>
     </row>
     <row r="231">
@@ -4127,7 +4127,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D231" t="n">
-        <v>-161.1183776855469</v>
+        <v>-159.6341400146484</v>
       </c>
     </row>
     <row r="232">
@@ -4143,7 +4143,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D232" t="n">
-        <v>-137.107421875</v>
+        <v>-141.8432464599609</v>
       </c>
     </row>
     <row r="233">
@@ -4159,7 +4159,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D233" t="n">
-        <v>-138.9957122802734</v>
+        <v>-132.4182891845703</v>
       </c>
     </row>
     <row r="234">
@@ -4175,7 +4175,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D234" t="n">
-        <v>-329.5495300292969</v>
+        <v>-318.7614135742188</v>
       </c>
     </row>
     <row r="235">
@@ -4191,7 +4191,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D235" t="n">
-        <v>-312.3096923828125</v>
+        <v>-319.5836791992188</v>
       </c>
     </row>
     <row r="236">
@@ -4207,7 +4207,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D236" t="n">
-        <v>-84.71974182128906</v>
+        <v>-82.12191009521484</v>
       </c>
     </row>
     <row r="237">
@@ -4223,7 +4223,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D237" t="n">
-        <v>-131.4025421142578</v>
+        <v>-132.4911041259766</v>
       </c>
     </row>
     <row r="238">
@@ -4239,7 +4239,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D238" t="n">
-        <v>-159.7365570068359</v>
+        <v>-167.2900848388672</v>
       </c>
     </row>
     <row r="239">
@@ -4255,7 +4255,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D239" t="n">
-        <v>-302.350341796875</v>
+        <v>-297.254150390625</v>
       </c>
     </row>
     <row r="240">
@@ -4271,7 +4271,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D240" t="n">
-        <v>-318.3893127441406</v>
+        <v>-331.8033142089844</v>
       </c>
     </row>
     <row r="241">
@@ -4287,7 +4287,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D241" t="n">
-        <v>-271.8551025390625</v>
+        <v>-272.3676147460938</v>
       </c>
     </row>
     <row r="242">
@@ -4303,7 +4303,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D242" t="n">
-        <v>-175.6520233154297</v>
+        <v>-177.1363372802734</v>
       </c>
     </row>
     <row r="243">
@@ -4319,7 +4319,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D243" t="n">
-        <v>-146.3340759277344</v>
+        <v>-145.2676086425781</v>
       </c>
     </row>
     <row r="244">
@@ -4335,7 +4335,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D244" t="n">
-        <v>-75.52070617675781</v>
+        <v>-78.53990936279297</v>
       </c>
     </row>
     <row r="245">
@@ -4351,7 +4351,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D245" t="n">
-        <v>-304.7420654296875</v>
+        <v>-301.2281799316406</v>
       </c>
     </row>
     <row r="246">
@@ -4367,7 +4367,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D246" t="n">
-        <v>-138.5524749755859</v>
+        <v>-139.7443542480469</v>
       </c>
     </row>
     <row r="247">
@@ -4383,7 +4383,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D247" t="n">
-        <v>-143.3119354248047</v>
+        <v>-134.8258666992188</v>
       </c>
     </row>
     <row r="248">
@@ -4399,7 +4399,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D248" t="n">
-        <v>-170.0558776855469</v>
+        <v>-165.1614837646484</v>
       </c>
     </row>
     <row r="249">
@@ -4415,7 +4415,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D249" t="n">
-        <v>-291.0371704101562</v>
+        <v>-291.744140625</v>
       </c>
     </row>
     <row r="250">
@@ -4431,7 +4431,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D250" t="n">
-        <v>-138.1547241210938</v>
+        <v>-140.1458892822266</v>
       </c>
     </row>
     <row r="251">
@@ -4447,7 +4447,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D251" t="n">
-        <v>-304.94921875</v>
+        <v>-304.1897583007812</v>
       </c>
     </row>
     <row r="252">
@@ -4463,7 +4463,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D252" t="n">
-        <v>-73.4420166015625</v>
+        <v>-76.67019653320312</v>
       </c>
     </row>
     <row r="253">
@@ -4479,7 +4479,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D253" t="n">
-        <v>-281.7220764160156</v>
+        <v>-286.0621948242188</v>
       </c>
     </row>
     <row r="254">
@@ -4495,7 +4495,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D254" t="n">
-        <v>-266.6170654296875</v>
+        <v>-277.0697631835938</v>
       </c>
     </row>
     <row r="255">
@@ -4511,7 +4511,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D255" t="n">
-        <v>-147.4794921875</v>
+        <v>-147.8277282714844</v>
       </c>
     </row>
     <row r="256">
@@ -4527,7 +4527,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D256" t="n">
-        <v>-86.43904113769531</v>
+        <v>-77.90627288818359</v>
       </c>
     </row>
     <row r="257">
@@ -4543,7 +4543,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D257" t="n">
-        <v>-87.78350830078125</v>
+        <v>-90.14113616943359</v>
       </c>
     </row>
     <row r="258">
@@ -4559,7 +4559,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D258" t="n">
-        <v>-90.58564758300781</v>
+        <v>-90.55662536621094</v>
       </c>
     </row>
     <row r="259">
@@ -4575,7 +4575,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D259" t="n">
-        <v>-80.89474487304688</v>
+        <v>-74.52512359619141</v>
       </c>
     </row>
     <row r="260">
@@ -4591,7 +4591,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D260" t="n">
-        <v>-282.143310546875</v>
+        <v>-271.3858337402344</v>
       </c>
     </row>
     <row r="261">
@@ -4607,7 +4607,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D261" t="n">
-        <v>-151.2852630615234</v>
+        <v>-149.6448974609375</v>
       </c>
     </row>
     <row r="262">
@@ -4623,7 +4623,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D262" t="n">
-        <v>-135.547119140625</v>
+        <v>-137.2550659179688</v>
       </c>
     </row>
     <row r="263">
@@ -4639,7 +4639,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D263" t="n">
-        <v>-156.1329803466797</v>
+        <v>-158.8795013427734</v>
       </c>
     </row>
     <row r="264">
@@ -4655,7 +4655,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D264" t="n">
-        <v>-143.0807647705078</v>
+        <v>-141.7696380615234</v>
       </c>
     </row>
     <row r="265">
@@ -4671,7 +4671,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D265" t="n">
-        <v>-145.7710266113281</v>
+        <v>-141.1734313964844</v>
       </c>
     </row>
     <row r="266">
@@ -4687,7 +4687,7 @@
         <v>0.9503057599067688</v>
       </c>
       <c r="D266" t="n">
-        <v>-82.22574615478516</v>
+        <v>-82.80809020996094</v>
       </c>
     </row>
     <row r="267">
@@ -4703,7 +4703,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D267" t="n">
-        <v>-232.3143920898438</v>
+        <v>-243.9723968505859</v>
       </c>
     </row>
     <row r="268">
@@ -4719,7 +4719,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D268" t="n">
-        <v>-141.3155975341797</v>
+        <v>-138.0095367431641</v>
       </c>
     </row>
     <row r="269">
@@ -4735,7 +4735,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D269" t="n">
-        <v>-283.4729614257812</v>
+        <v>-274.9277954101562</v>
       </c>
     </row>
     <row r="270">
@@ -4751,7 +4751,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D270" t="n">
-        <v>-160.0101165771484</v>
+        <v>-162.1915283203125</v>
       </c>
     </row>
     <row r="271">
@@ -4767,7 +4767,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D271" t="n">
-        <v>-160.3553619384766</v>
+        <v>-157.9370269775391</v>
       </c>
     </row>
     <row r="272">
@@ -4783,7 +4783,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D272" t="n">
-        <v>-144.6621551513672</v>
+        <v>-146.5335083007812</v>
       </c>
     </row>
     <row r="273">
@@ -4799,7 +4799,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D273" t="n">
-        <v>-299.4085693359375</v>
+        <v>-302.4164123535156</v>
       </c>
     </row>
     <row r="274">
@@ -4815,7 +4815,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D274" t="n">
-        <v>-305.798828125</v>
+        <v>-303.6943054199219</v>
       </c>
     </row>
     <row r="275">
@@ -4831,7 +4831,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D275" t="n">
-        <v>-297.4274597167969</v>
+        <v>-297.2198486328125</v>
       </c>
     </row>
     <row r="276">
@@ -4847,7 +4847,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D276" t="n">
-        <v>-150.6622314453125</v>
+        <v>-146.7866821289062</v>
       </c>
     </row>
     <row r="277">
@@ -4863,7 +4863,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D277" t="n">
-        <v>-152.84521484375</v>
+        <v>-154.6858520507812</v>
       </c>
     </row>
     <row r="278">
@@ -4879,7 +4879,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D278" t="n">
-        <v>-294.9675598144531</v>
+        <v>-290.0270080566406</v>
       </c>
     </row>
     <row r="279">
@@ -4895,7 +4895,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D279" t="n">
-        <v>-134.7876586914062</v>
+        <v>-139.5862274169922</v>
       </c>
     </row>
     <row r="280">
@@ -4911,7 +4911,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D280" t="n">
-        <v>-158.9713592529297</v>
+        <v>-164.1957092285156</v>
       </c>
     </row>
     <row r="281">
@@ -4927,7 +4927,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D281" t="n">
-        <v>-137.6859130859375</v>
+        <v>-137.2289733886719</v>
       </c>
     </row>
     <row r="282">
@@ -4943,7 +4943,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D282" t="n">
-        <v>-169.0038757324219</v>
+        <v>-164.7210083007812</v>
       </c>
     </row>
     <row r="283">
@@ -4959,7 +4959,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D283" t="n">
-        <v>-285.2640991210938</v>
+        <v>-281.8809509277344</v>
       </c>
     </row>
     <row r="284">
@@ -4975,7 +4975,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D284" t="n">
-        <v>-164.5867309570312</v>
+        <v>-163.0361938476562</v>
       </c>
     </row>
     <row r="285">
@@ -4991,7 +4991,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D285" t="n">
-        <v>-155.3450927734375</v>
+        <v>-146.5116882324219</v>
       </c>
     </row>
     <row r="286">
@@ -5007,7 +5007,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D286" t="n">
-        <v>-156.4065551757812</v>
+        <v>-156.9635772705078</v>
       </c>
     </row>
     <row r="287">
@@ -5023,7 +5023,7 @@
         <v>3.950075387954712</v>
       </c>
       <c r="D287" t="n">
-        <v>-260.8252563476562</v>
+        <v>-270.1922607421875</v>
       </c>
     </row>
     <row r="288">
@@ -5039,7 +5039,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D288" t="n">
-        <v>-143.9919281005859</v>
+        <v>-146.2906341552734</v>
       </c>
     </row>
     <row r="289">
@@ -5055,7 +5055,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D289" t="n">
-        <v>-150.1417541503906</v>
+        <v>-149.3773498535156</v>
       </c>
     </row>
     <row r="290">
@@ -5071,7 +5071,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D290" t="n">
-        <v>-146.9758148193359</v>
+        <v>-146.8098602294922</v>
       </c>
     </row>
     <row r="291">
@@ -5087,7 +5087,7 @@
         <v>1.950151324272156</v>
       </c>
       <c r="D291" t="n">
-        <v>-138.5732574462891</v>
+        <v>-131.5228271484375</v>
       </c>
     </row>
   </sheetData>
